--- a/website/assets/files/Program Questionnaire Data Export 2025.xlsx
+++ b/website/assets/files/Program Questionnaire Data Export 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pajak_hc\Work Folders\Desktop\Heather's Folders\Data Call\FY2025 Data Call\Website\Datasets\Exports of Questionnaires\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C176C5-D33D-445E-BCE1-22D1D0602365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9194112C-E5C1-4CD1-81E1-02FC25AC2659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2490" windowWidth="29040" windowHeight="15720" xr2:uid="{5CCCF484-60C7-4BD0-8203-0FB10432C6A2}"/>
   </bookViews>
@@ -1693,12 +1693,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">The agency has many of the essential components needed to reduce improper payments and unknown payments. While HUD made remarkable strides in fiscal year (FY) 2025, significant issues still remain and enhancements in human capital, information systems, and infrastructure are needed to continue to improve payment integrity. HUD launched Project Voucher, a whole-of-agency transformation effort to improve the integrity and efficiency of its rental assistance programs. The initiative aims to eliminate fraud, waste, and abuse, maximize resources, and ensure responsible stewardship of taxpayer dollars, while establishing greater visibility and traceability in rental assistance payments. This initiative would enable improved collection, management, and assessment of critical tenant eligibility information and documentation, such as proof of identify, housing, income, assets, applicable income deductions, and complete HUD forms for applicable participants. HUD is also conducting a study to confirm that its programs are using taxpayer dollars for the correct purpose. The study includes gathering data and information that links the impact of the taxpayer dollars spent for each program to the outcomes for people who benefit from HUD's programs related to affordable housing, poverty, and other measures. Together, these projects will aim to further reveal the additional internal controls, human capital, information systems, and other policy and infrastructure needs required to reduce improper and unknown payments. 
-By strengthening these areas, the agency aims to achieve a level of reduction in unknown payments that justifies the associated expenditures. This approach ensures that the cost of implementing further controls do not exceed the savings gained from preventing or recovering improper payments. These projects represent a significant commitment to enhancing program integrity, preventing future payment errors, and ensuring federal funds are allocated to U.S. citizens and eligible non-citizens. 
-The Department is actively prioritizing resources to address payment integrity objectives under Project HUD Unified Grant System (HUGS) and Project Voucher. Project HUGS and Project Voucher are designed to deliver full transparency into the flow of HUD funds, tracing dollars from the Department all the way to the ultimate beneficiary, whether a family receiving rental assistance, a developer building affordable housing, or a nonprofit providing services. The end result of this effort is continuous financial monitoring that allows HUD to move beyond episodic reviews and instead embed accountability and financial best practices into day-to-day operations. By streamlining processes and integrating modern analytics, HUD will generate more timely and accurate financial reporting while strengthening its payment integrity program. Powered by machine learning and advanced analytics, this approach enables HUD to detect anomalies, predict risks, and proactively safeguard funds with a level of precision and scale not possible through manual oversight, ensuring that funds are used as intended.
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">The Department is actively prioritizing resources to address payment integrity objectives under Project HUD Unified Grant System (HUGS) and Project Voucher. Project HUGS and Project Voucher are designed to deliver full transparency into the flow of HUD funds, tracing dollars from the Department all the way to the ultimate beneficiary, whether a family receiving rental assistance, a developer building affordable housing, or a nonprofit providing services. The end result of this effort is continuous financial monitoring that allows HUD to move beyond episodic reviews and instead embed accountability and financial best practices into day-to-day operations. By streamlining processes and integrating modern analytics, HUD will generate more timely and accurate financial reporting while strengthening its payment integrity program. Powered by machine learning and advanced analytics, this approach enables HUD to detect anomalies, predict risks, and proactively safeguard funds with a level of precision and scale not possible through manual oversight, ensuring that funds are used as intended.
 </t>
   </si>
@@ -1737,25 +1731,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">To address the causes of unknown payments and prevent future unknown payments, a series of corrective actions have been taken and planned for fiscal year (FY) 2026. 
-In FY 2025 HUD introduced innovative methods and advanced analytics to evaluate tenant and recipient records. This approach allowed HUD to analyze millions of payment records from FY 2024, rather than relying on traditional sampling of just a few hundred records. As a result, HUD gained greater insights into potential risks and issues while identifying problematic records and estimating payments errors. This analytical strategy enables HUD to detect eligibility and payment errors more effectively as well as address the disbursement of funding design and complex eligibility and program requirements, which increases the risk of payment errors. 
-For the first time, HUD evaluated all tenant records across the rental assistance programs, uncovering eligibility issue  totaling  billions in unknown Tenant-Based Rental Assistance (TBRA) payments.
-HUD immediately took action to remediate these findings. During FY 2025 the Office of Public and Indian Housing (PIH) strengthened controls with pre-award verifications to improve SAM.gov registration status, ensuring that funds were not paid to ineligible entities. HUD also reestablished its Computer Matching Agreement with the Department of the Treasury as of May 1, 2025, and is working to enable near-real-time eligibility verification through the Treasury Do Not Pay verification portal. HUD already realized the benefits of Treasury’s Do Not Pay databases, referencing the databases to flag over $69 million in payments made on behalf of deceased tenants in FY 2024 under the TBRA program. Further, PIH is actively investigating the approximately $1.5 billion of unknown payments to take corrective action and prevent further issues. 
-This year, HUD conducted its first collaboration with the Department of Homeland Security to identify potential ineligible non-citizens receiving rental assistance in the Section 8 and Section 9 portfolio, including the Operating Fund, TBRA and PBRA programs. A total of 8.8 million tenant records were analyzed, confirming U.S. citizenship and non-citizen eligibility for 8.6 million citizen and non-citizen eligible tenants. The analysis of the records indicates that thousands of ineligible non-citizens are potentially receiving assistance under the programs. 
-The OCFO established the Strike Force to enhance efforts in eliminating fraud, corruption, and immigration violations within Public Housing Agencies (PHAs) as mandated by new regulations. To fulfill these mandates, the Strike Force utilizes publicly available information, compiles data from across HUD and identifies potential risk factors associated with PHAs and their personnel. This analysis enables the team to compile detailed, preliminary risk assessments and intelligence reports and present them to the appropriate law enforcement agency, expediting the detection and resolution of possible misconduct. 
-HUD also launched Project Voucher, a whole-of-agency transformation effort to improve the integrity and efficiency of its rental assistance programs. The initiative aims to eliminate fraud, waste, and abuse, maximize resources, and ensure responsible stewardship of taxpayer dollars, while establishing greater visibility and traceability in rental assistance payments. Additionally, HUD is conducting a study to confirm that its programs are using taxpayer dollars for the correct purpose. The study includes gathering data and information that links the impact of the taxpayer dollars spent for each program to the outcomes for people who benefit from HUD's programs related to affordable housing, poverty, and other measures. HUD's comprehensive reviews, Project Voucher, and research efforts represent a significant commitment to enhance program integrity, prevent future payment errors, and ensure federal funds are allocated to those who genuinely need assistance. 
-In FY 2026, HUD plans to continue the progress made in FY 2025. By increasing its use of automation tools designed to identify SAM.gov registrations expired or soon to be expired, prior to processing payments, HUD aims to further reduce the risk of payments being made to ineligible entities. Additionally, performing near-real-time eligibility verification through the Treasury Do Not Pay verification portal will enhance HUD’s ability to reduce fraud and prevent improper payments. With Project Voucher and research efforts, HUD is paving the way for a more accountable and transparent rental assistance system. Further, Strike Force investigations will aim to reveal opportunities for greater accountability across PHAs. Ultimately, the greater visibility into the unknown payments has enabled HUD to begin to design technology, process, and policy improvements that will strengthen its payment integrity programs in the long-run. 
-The planned and completed actions in the corrective action plan are strategically designed to address the root causes of HUD's unknown payments, reflecting a proportional response to the severity of these issues. For example, the Office of Public and Indian Housing strengthened controls with pre-award verifications to improve SAM.gov registration status, ensuring that funds were not paid to ineligible entities. Additionally, performing near-real-time eligibility verification through the Treasury Do Not Pay verification portal will enhance HUD’s ability to reduce fraud and prevent improper payments. For example, the insights gained from Do Not Pay have enabled HUD to investigate $69 million of unknown payments made on behalf of deceased tenants. The Office of the Chief Financial Officer (OCFO) established the Strike Force to enhance efforts in eliminating fraud, corruption, and immigration violations within Public Housing Agencies (PHAs) as mandated by new regulations. The agency’s Project Voucher transformation effort also aims to bring greater visibility and traceability in rental assistance payments. 
-Overall, greater collaboration and visibility into payment and tenant data enables HUD to comprehensively identify unknown payments and generate targeted remediation strategies to address the severity of the issues identified. This multifaceted strategy not only aims to rectify existing problems identified from payments made in FY 2024 but also establishes mechanisms for preventing future occurrences.
-</t>
-  </si>
-  <si>
     <t>Cross Enterprise Sharing, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In HUD’s Audit Management Systems (AMS), Headquarters’ Primary Organization Heads (HPOHs) assign Program Office Management Points of Contact and Audit Liaison Officers to manage Single Audit Act (SAA) responsibilities. Assigned Program staff are responsible for developing and submitting management letters to auditees regarding resolution findings in their single audit report associated with an Assistance Listing Number (ALN) and working with auditees to ensure reports are submitted timely and findings are resolved. Audit Liaison Officers are responsible for approving the closure of findings where applicable. Audits are performed in accordance with the Single Audit Act (31 U.S.C. Chapter 75) and the Uniform Guidance audit requirements in 2 CFR Part 200, Subpart F, which govern how federal award recipients are evaluated by independent auditors. The submission, monitoring, and tracking of findings resulting from these audit reports are under the direct authority and responsibility of each applicable HPOH and are tracked in HUD's audit tracking system's SAA module. HUD’s Departmental Single Audit Act policy requires all program offices to use the SAA module for documenting and tracking Single Audit reviews. SAA audits can involve more than one program, agency, or State and local governments, etc. Entities receiving federal financial assistance may be required to have an audit performed in accordance with the SAA of 1984 as amended and the OMB Circular A-133. 
-HUD also conducts program oversight through the Section Eight Management Assessment Program (SEMAP), a system used by HUD to measure the performance of Public Housing Agencies (PHAs) that administer the Housing Choice Voucher (HCV) Program.
-</t>
   </si>
   <si>
     <t xml:space="preserve">The planned and completed actions in the corrective action plan are strategically designed to address the root causes of HUD's unknown payments, reflecting a proportional response to the severity of these issues. For example, the Office of Public and Indian Housing strengthened controls with pre-award verifications to improve SAM.gov registration status, ensuring that funds were not paid to ineligible entities. Additionally, performing near-real-time eligibility verification through the Treasury Do Not Pay verification portal will enhance HUD’s ability to reduce fraud and prevent improper payments. For example, the insights gained from Do Not Pay have enabled HUD to investigate $69 million of unknown payments made on behalf of deceased tenants. The Office of the Chief Financial Officer (OCFO) established the Strike Force to enhance efforts in eliminating fraud, corruption, and immigration violations within Public Housing Agencies (PHAs) as mandated by new regulations. The agency’s Project Voucher transformation effort also aims to bring greater visibility and traceability in rental assistance payments. 
@@ -2148,24 +2124,6 @@
 We will continue our quality reviews and cost-effective program integrity work including medical continuing disability reviews.
 Improper payments within the agency’s control are due to our failure to take timely and proper actions.  To address these improper payments, we are investing in information technology modernization to provide our employees with user-friendly systems and tools to better serve the public, including a single unified process for benefit applications and a consolidated source with all information and agency interactions with our customers.  To meet the challenges of our growing workloads and provide the best service possible, we are streamlining our policies and procedures, issuing reminders to technicians, and automating more of our business processes.  We will continue to issue periodic reminders and policy clarifications, as needed.
 There are some DI improper payments that have historically been caused by actions both outside of and within agency control.  For example, the Social Security Act used to include two provisions – the Windfall Elimination Provision (WEP) and Government Pension Offset (GPO) – that reduced or offset Social Security monthly benefits to beneficiaries who receive a pension based on non-covered earnings.  On January 5, 2025, the Social Security Fairness Act of 2023 was signed into law, thereby repealing WEP/GPO.  December 2023 is the last month that WEP and GPO will apply.  This means that those rules no longer apply to benefits payable for January 2024 and later.  We anticipate the WEP/GPO repeal will significantly reduce and eventually eliminate WEP/GPO improper payments in future years.</t>
-  </si>
-  <si>
-    <t>We developed the Improper Payment Alignment Strategy (IPAS) process to obtain agency-wide engagement and agreement on corrective actions to address the root causes of improper payments and the top deficiencies in our programs.  We have completed IPASs on multiple areas of Disability Insurance (DI) improper payment deficiency, and we monitor the corrective actions within those IPASs.  Most of the corrective actions described within this response are from two new IPASs we completed in FY 2025 (computations and relationship/dependency) as well as IPASs on substantial gainful activity (SGA), windfall elimination provision (WEP) and government pension offset (GPO), and improving death data processes.  We also discuss broad-based efforts to ensure policy compliance and payment accuracy and ensure individuals receive the benefits they are due.
-SGA is the performance of significant physical or mental activities in work for pay or profit, or in work of a type generally performed for pay or profit, regardless of the legality of the work.  Beneficiaries are required to report changes in their work activity and increases in earnings to ensure proper payments and continued eligibility for benefits.  Improper payments based on SGA are a leading cause of improper payments in the OASDI program; most occurring as a result of beneficiaries or representative payees failing to report changes in work.
-To reduce our reliance on beneficiary and representative payee reporting of employment and wage information, we published the Use of Electronic Payroll Data To Improve Program Administration final rule in December 2024.  Through the process known as the payroll information exchange (PIE), we obtain wage and employment information from a commercial payroll data provider for individuals who have provided authorization.  On April 7, 2025, we began the phased implementation of PIE with an initial exchange of 1 million Social Security numbers (SSN).  We gradually increased the exchanges each month until reaching full implementation of 10.7 million SSNs in September 2025.  We continued monthly exchanges with the full authorized population after September.  As part of the PIE implementation activities, we provided training to technicians, updated our policies and instructions, and released communication to the public.  In FY 2026 and beyond, we will implement measures to increase PIE authorizations; develop requirements for requesting historical wage data through PIE; develop a process for handling SSNs that are flagged for name mismatch and excluded from subsequent changes; streamline and improve notices, forms, and receipts related to PIE based on customer experience feedback; develop and implement enhanced management information; mismatch exclusions; and other enhancements.  PIE will improve payment accuracy, reduce improper payments, and reduce the reporting burden on individuals when they authorize us to obtain this information through an information exchange, and we receive it.  We also anticipate that implementation will result in more efficient use of our limited administrative resources because our technicians would reduce the amount of time they spend manually requesting this information from payroll data providers and employers; manually entering data into our systems from an individual’s pay records; contacting individuals; and assisting individuals with the results of incomplete or untimely reporting.
-For individuals or employers not participating in PIE, we continue to offer electronic wage reporting tools, such as the myWageReport (myWR) online tool.  myWR allows Disability Insurance beneficiaries, Supplemental Security Income (SSI) recipients, concurrent beneficiaries, and representative payees to report wages and view, print, or save a receipt.  Self-reporters and their representative payees can report wages that occurred within a two-year timeframe from the reporting date.  From April-May 2025, we released social media posts on Facebook and X sharing a link to our YouTube video to help beneficiaries learn why it is important to report wages and the automated electronic options for wage reporting.  This included instructional videos with step-by-step instructions on how to use the agency’s self-reporting wage applications.  In FY 2026, we will continue to use our social media channels to post reminders for our beneficiaries about the importance of promptly reporting changes that impact their eligibility and payment amounts.  These posts will inform beneficiaries how we are required by law to adjust payments or recover debts when people receive payments they are not entitled to.
-In July 2025, we started a national Targeted Work Review Process (TWRP) for specific work continuing disability reviews (CDR).  The TWRP leverages the expertise of a cadre of technicians to use readily available earnings data to formulate a proposed work CDR decision prior to requesting work activity report.  Technicians will send both the work activity report and due process notice simultaneously.  The TWRP aims to reduce work CDR processing time by allowing one technician to process the case from start to finish and reducing delays in sending/receiving evidence.  TWRP continued into early FY 2026, and we plan to evaluate its outcomes later in FY 2026.  We are also developing a new Electronic Work Continuing Disability Review (eWCDR) application to replace and modernize the system technicians use to process CDRs based on work activity.  The new system will enforce policy and best practices with an intuitive user interface and will eliminate current system limitations that lead to large improper payments through delays and processing errors.  The application will streamline the disability review process and will have a positive impact in reducing substantial gainful activity improper payments.  In FY 2025, efforts continued to develop eWCDR capabilities that allow technicians to receive beneficiaries’ reports of work, document and evaluate pay stubs and self-employment income, mail out forms and notices, and collect Management Information.  We plan to release the minimum viable product to technicians by the end of FY 2026.  We also use WorkSmart, a tool that helps identify DI beneficiaries whose earnings may place them at risk of overpayment.  WorkSmart continues to alert cases for work CDRs based on available earnings data.  In addition, with the appropriate authorization, WorkSmart will utilize PIE data to identify and alert cases that may require a work CDR.
-We complete Work CDR Quality Reviews to ensure compliance with policy and the Bipartisan Budget Act (BBA) of 2015 by evaluating a monthly, stratified random sample of processed Work CDRs.  This review captures processing times, assesses Trust Fund impact from policy non-compliance, measures accuracy rates, identifies procedural and training improvements, and collects data on new processing procedures.  We provide case-level feedback and share the broader data analysis with stakeholders.  We completed data analysis of FY 2023 and FY 2024 reviews and plan to publish them in FY 2026.  We are planning the FY 2026 review to evaluate Work CDR accuracy amid the implementation of PIE and other procedural changes.
-To improve understanding and reduce the burden on our customers and their employers, we are updating several disability-related forms.  In February 2025, we published a revised SSA-3033, Employee Work Questionnaire, and clarified policy and procedures for technicians developing subsidy for DI and SSI initial claims, and DI work continuing disability reviews.  The Office of Management and Budget (OMB) approved the SSA-821 Work Activity Report in July 2025, which we published in September 2025.  The revised SSA-820 Self-Employment Work Activity Report is currently pending OMB approval; we expect completion of the form in FY 2026.
-WEP and GPO reduced or offset Social Security monthly benefits to beneficiaries who received a pension based on non-covered earnings.  Most of these workers had non-covered earnings from federal, state, or local governments.  Errors relating to WEP/GPO have been one of the leading causes of OASI improper payments.  We had previously relied on applicants, beneficiaries, or their representative payees to report their entitlement to current or future non-covered pensions; however, they did not always report the receipt of or changes to a pension, resulting in benefit calculation and payment errors.  WEP and GPO errors also occurred when the agency did not correctly impose reductions or offset, misapplied exceptions or exemptions, or applied WEP but not GPO (or vice versa) for dually entitled beneficiaries.
-We developed a comprehensive corrective action plan to address multiple underlying causes of WEP/GPO improper payments.  We assessed the root causes of improper payments based on these changes and developed policy, data, systems, and training solutions in line with each of the root causes of improper payments.  On January 5, 2025, the Social Security Fairness Act of 2023 was signed into law, thereby repealing WEP/GPO.  December 2023 is the last month that WEP and GPO will apply.  This means that those rules no longer apply to benefits payable for January 2024 and later.  The agency worked quickly and successfully to implement these changes.  As of July 7, 2025, we completed sending over 3.1 million payments, totaling $17 billion, to beneficiaries eligible under the Social Security Fairness Act.  The average retroactive payment was $7,208.  As of September 30, 2025, we have taken over 387,000 new initial claims.  We began releasing higher monthly benefit payments in April 2025.  We anticipate the WEP/GPO repeal will significantly reduce and eventually eliminate WEP/GPO improper payments in future years.
-Computational errors occur due to many factors.  Generally, these factors include: systems limitations for complex cases; manual calculation of benefits involving complicated policies; technician errors; incorrect earnings postings; beneficiaries not reporting complete and pertinent information; and lack of accurate and accessible data.  We developed processes using UIPath software to create automated “robotic” programs that perform routine or repetitive tasks and increase the speed and accuracy of manual processing.  Robotic Processing Automation (RPA), or “BOTs,” are available to Processing Center (PC) technicians to assist with processing manual awards or post-entitlement actions.  Since January 2021, seven PC-specific BOTs have been created to assist with DI and Old-Age and Survivors actions and placed into production.  In December 2024, we provided general reminders and guidance for PC technicians on BOT usage.  We completed the final testing stages of the UiPath Assistant software and rolled out the new platform to PC users in August 2025.  We are making a long-term investment in robotics technology using the software to improve business processes and eliminate manual actions.
-In January 2025, we released instructions to field office technicians to review earning records for identified pending retirement and disability claims.  Validating earnings records associated with pending claims ensures accurate eligibility and payment amounts.  In April 2025, we released a reminder to frontline technicians including information on reducing improper payments related to benefit computations.  When automated systems cannot compute benefit amounts in certain situations, there are a variety of computations tools that technicians should use to ensure accuracy.  In May 2025, we updated policy instructions associated with temporary and ongoing earnings inaccuracies and coding used to trigger an alert for technicians to review and ensure the accuracy of earnings records and Primary Insurance Amounts before automatic benefit increases.  In the May 2025 policy update, we expanded the coding to include “all disclaimed wages and those institutionalized.”  This action stemmed from an Office of the Inspector General report on institutionalized beneficiaries who have earnings.
-The Federal Employee Compensation Act (FECA) provides income and medical cost protection to covered Federal civilian employees injured on the job, employees who have incurred a work-related injury or occupational disease and beneficiaries of employees whose death is attributable to a job-related injury or occupational disease.  FECA is administered by the Department of Labor (DOL), and receipt of FECA benefits can offset DI benefits.  In December 2023, we established a Memorandum of Understanding with DOL for use of an employee compensation portal.  Technicians can submit individual real-time queries in the portal to obtain FECA data and complete computations.  We continue to explore data exchange opportunities that would improve efficiency and accuracy of related computations by eliminating the need for a manual query and transition to a batch process.  We are working to complete the computer matching agreement and will begin implementation of the data exchange in FY 2026 should funding be available.
-Marital status and child relationship factors are material when determining entitlement to certain auxiliary and survivor benefits.  Improper payments occur due to beneficiaries failing to report changes in marital status, the agency’s inability to automate, and difficulty expanding data exchanges to include the exchange of marital information.  To address these issues, in FY 2025, we have been airing relationship and dependency reminders on televisions in field office reception areas.  In April 2025, we released a reminder to frontline technicians on checking for program entitlement when an individual changes their name due to marriage or divorce.  The guidance also included a reminder on verifying that all child-in-care information is entered in the system correctly.  In FY 2026, if resources allow, we will explore options to expand the Internet Social Security Number Replacement’s current process and incorporate downstream application alerts to reduce instances of improper payments.
-We collect death data from a variety of sources and work to improve our death data processing so that we can effectively administer our programs.  We have a contract with every State Bureau of Vital Statistics (the custodians for death records) and with some jurisdictions to provide us death data.  Since 2002, we worked with States that want and are able to build a streamlined death registration process known as Electronic Death Registration (EDR).  As of July 2025, all 50 States, New York City, Washington, D.C., Puerto Rico, and the Commonwealth of the Northern Mariana Islands report deaths through the EDR process.  On September 30, 2024, we awarded a contract with the National Association for Public Health Statistics and Information Systems (NAPHSIS) on the acquisition of historical State death records.  In FY 2025, we worked with NAPHSIS on establishing the infrastructure required to receive the historical death data.  This multi-year effort will increase the accuracy, integrity, and completeness of our death data.
-In March and June 2025, we updated Numident records with additional death information for non-beneficiary individuals that were over 120 years of age when there was no death record present on the Numident.  These efforts resulted in over 12 million death records being added to the Numident.  In March 2025, we also provided the Internal Revenue Service a one-time file concerning individuals listed in the agency’s enumeration system who are age 120 or older based on available information as recorded in that system.  Efforts are ongoing to update our Numident records for individuals over 100 years of age with death data.  We also increased the frequency with which the agency provides updates concerning the full file of death information to the Bureau of the Fiscal Service for use in the Do Not Pay system.? We implemented this change (from weekly to daily) on April 1, 2025.  In July 2025, we released a reminder to field office technicians to verify and record the death when a report of death on form DS-2060 U.S. Consular Report of Death Abroad is received.
-For root causes where the data or information needed to process a payment correctly does not exist or the agency is u</t>
   </si>
   <si>
     <t>Training, Predictive Analytics, Cross Enterprise Sharing, Behavioral/Psych Influence, Automation, Audit</t>
@@ -2234,24 +2192,6 @@
 There are some Old-Age and Survivors Insurance program improper payments that have historically been caused by actions both outside of and within agency control.  For example, the Social Security Act used to include two provisions – the Windfall Elimination Provision (WEP) and Government Pension Offset (GPO) – that reduced or offset Social Security monthly benefits to beneficiaries who receive a pension based on non-covered earnings.  On January 5, 2025, the Social Security Fairness Act of 2023 was signed into law, thereby repealing WEP/GPO.  December 2023 is the last month that WEP and GPO will apply.  This means that those rules no longer apply to benefits payable for January 2024 and later.  We anticipate the WEP/GPO repeal will significantly reduce and eventually eliminate WEP/GPO improper payments in future years.</t>
   </si>
   <si>
-    <t>We developed the Improper Payment Alignment Strategy (IPAS) process to obtain agency-wide engagement and agreement on corrective actions to address the root causes of improper payments and the top deficiencies in our programs.  We have completed IPASs on multiple areas of Old-Age and Survivors Insurance (OASI) improper payment deficiency, and we monitor the corrective actions within those IPASs.  Most of the OASI corrective actions described within this response are from two new IPASs completed in FY 2025 (computations and relationship/dependency) as well as IPASs on windfall elimination provision (WEP) and government pension offset (GPO) and improving death data processes.  We also discuss broad-based efforts to ensure policy compliance and payment accuracy and ensure individuals receive the benefits they are due.
-WEP and GPO reduced or offset Social Security monthly benefits to beneficiaries who received a pension based on non-covered earnings.  Most of these workers had non-covered earnings from federal, state, or local governments.  Errors relating to WEP/GPO have been one of the leading causes of OASI improper payments.  We had previously relied on applicants, beneficiaries, or their representative payees to report their entitlement to current or future non-covered pensions; however, they did not always report the receipt of or changes to a pension, resulting in benefit calculation and payment errors.  WEP and GPO errors also occurred when the agency did not correctly impose reductions or offset, misapplied exceptions or exemptions, or applied WEP but not GPO (or vice versa) for dually entitled beneficiaries.  
-We developed a comprehensive corrective action plan to address multiple underlying causes of WEP/GPO improper payments.  We assessed the root causes of improper payments based on these changes and developed policy, data, systems, and training solutions in line with each of the root causes of improper payments.  On January 5, 2025, the Social Security Fairness Act of 2023 was signed into law, thereby repealing WEP/GPO.  December 2023 is the last month that WEP and GPO will apply.  This means that those rules no longer apply to benefits payable for January 2024 and later.  The agency worked quickly and successfully to implement these changes.  In April, we began releasing higher monthly benefit payments.  As of July 7, 2025, we completed sending over 3.1 million payments, totaling $17 billion, to beneficiaries eligible under the Social Security Fairness Act.  The average retroactive payment was $7,208.  As of September 30, 2025, we have taken over 387,000 new initial claims.  We anticipate the WEP/GPO repeal will significantly reduce and eventually eliminate WEP/GPO improper payments in future years.
-Computational errors occur due to many factors.  Generally, these factors include:  systems limitations for complex cases; manual calculation of benefits involving complicated policies; technician errors; incorrect earnings postings; beneficiaries not reporting complete and pertinent information; and lack of accurate and accessible data.  We continue development of the Consolidated Claims Experience (CCE), a modernized user-friendly web-based application designed to centralize and streamline benefit claim processing actions, reduce training time for technicians, and provide a more intuitive approach for data collection and processing of benefit claims.  CCE will employ modernized and enhanced computation utilities that minimize manual tasks and help technicians identify entitlement and eligibility for all programs for which the claimant qualifies, in order to mitigate missed entitlements.  The system introduces new and enhanced features not found in existing platforms, such as More Info links, talking points for users, and easy access to commonly used external resources.  These improvements increase customer satisfaction by eliminating redundant information requests and reducing the need for technicians to recontact customers, improve the timeliness and accuracy of claims processing, enhancing efficiency, and reducing operating costs.  Between December 2024-August 2025, we released the retirement (RIB), Medicare-Only, and RIB with Medicare applications and user-requested enhancements in CCE to 14 sites in the Northeast and Mid-West/West regions.? We released these three applications nationally in CCE in September 2025.
-We developed processes using UIPath software to create automated “robotic” programs that perform routine or repetitive tasks and increase the speed and accuracy of manual processing.  Robotic Processing Automation (RPA), or “BOTs,” are available to Processing Center (PC) technicians to assist with processing manual awards or post-entitlement actions.  Since January 2021, seven PC-specific BOTs have been created to assist with OASI and/or Disability Insurance actions and placed into production.  In December 2024, we provided general reminders and guidance for PC technicians on BOT usage.  We completed the final testing stages of the UiPath Assistant software and rolled out the new platform to PC users in August 2025.  We are making a long-term investment in robotics technology using the software to improve business processes and eliminate manual actions.
-In January 2025, we released instructions to field office technicians to review earning records for identified pending retirement and disability claims.  Validating earnings records associated with pending claims ensures accurate eligibility and payment amounts.  In April 2025, we released a reminder to frontline technicians including information on reducing improper payments related to benefit computations.  When automated systems cannot compute benefit amounts in certain situations, there are a variety of computations tools that technicians should use to ensure accuracy.  In May 2025, we updated policy instructions associated with temporary and ongoing earnings inaccuracies and coding used to trigger an alert for technicians to review and ensure the accuracy of earnings records and Primary Insurance Amounts before automatic benefit increases.  In the May 2025 policy update, we expanded the coding to include “all disclaimed wages and those institutionalized.”  This action stemmed from an Office of the Inspector General report on institutionalized beneficiaries who have earnings.
-Marital status and child relationship factors are material when determining entitlement to certain auxiliary and survivor benefits.  Improper payments occur due to beneficiaries failing to report changes in marital status, the agency’s inability to automate, and difficulty expanding data exchanges to include the exchange of marital information.  To address these issues, in FY 2025, we have been airing relationship and dependency reminders on televisions in field office reception areas.  In April 2025, we released a reminder to frontline technicians on checking for program entitlement when an individual changes their name due to marriage or divorce.  The guidance also included a reminder on verifying that all child-in-care information is entered in the system correctly.  In FY 2026, if resources allow, we will explore options to expand the Internet Social Security Number Replacement’s current process and incorporate downstream application alerts to reduce instances of improper payments.  
-We collect death data from a variety of sources and work to improve our death data processing so that we can effectively administer our programs.  We have a contract with every State Bureau of Vital Statistics (the custodians for death records) and with some jurisdictions to provide us death data.  Since 2002, we worked with States that want and are able to build a streamlined death registration process known as Electronic Death Registration (EDR).  As of July 2025, all 50 States, New York City, Washington, D.C., Puerto Rico, and the Commonwealth of the Northern Mariana Islands report deaths through the EDR process.  On September 30, 2024, we awarded a contract with the National Association for Public Health Statistics and Information Systems (NAPHSIS) on the acquisition of historical State death records.  In FY 2025, we worked with NAPHSIS on establishing the infrastructure required to receive the historical death data.  This multi-year effort will increase the accuracy, integrity, and completeness of our death data.  
-In March and June 2025, we updated Numident records with additional death information for non-beneficiary individuals that were over 120 years of age when there was no death record present on the Numident.  These efforts resulted in over 12 million death records being added to the Numident.  In March 2025, we also provided the Internal Revenue Service a one-time file concerning individuals listed in the agency’s enumeration system who are age 120 or older based on available information as recorded in that system.  Efforts are ongoing to update our Numident records for individuals over 100 years of age with death data.  We also increased the frequency with which the agency provides updates concerning the full file of death information to the Bureau of the Fiscal Service for use in the Do Not Pay system.? We implemented this change (from weekly to daily) on April 1, 2025.  In July 2025, we released a reminder to field office technicians to verify and record the death when a report of death on form DS-2060 U.S. Consular Report of Death Abroad is received.
-For root causes where the data or information needed to process a payment correctly does not exist or the agency is unable to access the data or information needed, we are establishing alternate sources of information.  For example, we conducted 22 computer-matching agreements (CMA) with various Federal partners to help us determine eligibility and offset benefits for our programs.  The total annual savings attributed to these CMAs is approximately $14.9 billion, with an annual cost of approximately $510 million, yielding a positive benefit-to-cost ratio of about $29 to $1.  We plan to continue current CMAs that yield a positive cost-benefit ratio, expand effective CMAs to meet additional program needs, research current programs, work with internal stakeholders to identify data exchange needs, and pursue new data exchanges with potential partners.  In December 2024 and April 2025, we held Data Exchange Community of Practice meetings.  In FY 2026, we are working to reestablish the relationships with the current agency contacts, update the invitation list, and determine future topics for the meetings as resources allow.
-We have several broad-based initiatives in place or underway that are designed to ensure technician compliance with policy and improve payment accuracy.
-We complete Transaction Accuracy Reviews (TAR) on a triennial basis to assist in assessing operational quality.  TAR focuses on a review of the nonmedical factors of entitlement and eligibility for OASI and DI payments in initial claims awards and disallowances.  TAR findings provide insight to causes of improper payments and identify recommendations for improvement, which are shared with agency stakeholders.  TAR is completed on a triennial basis.  We will complete the next TAR report in FY 2027 based on reviews of FY 2026 case samples.
-In September 2024, we released the 21st Century PolicyNet (21CPN), which replaced PolicyNet, the 20+ year-old software platform that contains multiple applications and hosts tens of thousands of pages of policy instruction.  The overall goals of 21CPN are an improved user experience, process efficiencies for the author, publisher, and researcher role, as well as improving searching capabilities, including the use of intelligent search.  In December 2024, we launched improvements that introduced new message types, enhanced search functionalities, upgraded navigation features, included spell check for technician searches, and provided access to a variety of operational resources, archives, and margin notes.  In April 2025, we successfully finished the data migration process and implemented enhanced search features.  These improvements now encompass the hearings, appeal, and litigation law manual, as well as Social Security rulings and acquiescence rulings, along with policy documents and ownership details.  Additionally, we provided quick access to agency form repositories and included a user guide for 21CPN.  In June 2025, we launched an advanced search feature designed to improve the accessibility of policies, procedures, and instructions.  Additionally, we upgraded the application's presentation and usability by incorporating a series of content clusters and a "Trending" topics section to showcase and highlight agency initiatives for key stakeholders.  In September 2025, we broadened the data set to incorporate various procedural content clusters, link libraries, question and answer sections, and related instructions links.  Furthermore, we improved the presentation functionality by introducing subscriptions and daily messages.  Finally, by the end of FY 2026, contingent upon successful testing and evaluation, we plan to launch a generative artificial intelligence (AI) "Policy Assistant Tool (PAT)" designed to simplify the search process for policies, procedures, and instructions.  This tool will assist technicians in quickly and accurately finding and understanding relevant information to aid in decision-making.
-We developed the Technician Experience Dashboard (TED) as an enterprise customer relationship management solution that will provide a single location for information about our customers’ interactions with the agency to make it easier for our employees to help the public and increases efficiency and accuracy, improving the overall customer experience.  In February 2024, we rolled TED out nationally to all field offices (FO) and workload support units.  In November 2024, we expanded TED to all teleservice (TSC) centers.  TED modernized the previous 30-year-old Customer Help and Information Program (CHIP) that assisted TSC technicians when responding to customer inquiries via telephone.  In January and March 2025, we released two iterations of TED enhancements, improving upon the functionality for field office and teleservice centers.  In April and June 2025, we enhanced the identity verifications procedures within TED to send a Security Authentication Personal Identification Number to authenticated customers (that technicians subsequently verify) before making direct deposit and direct express enrollments, changes, or cancellations over the phone.  
-In December 2025, we plan to release a workflow in TED that allows FO and TSC technicians to update payment information for Supplemental Security Income (SSI) recipients.  The release will also include the FO expansion of the ability to automate the process for collecting the customer SSN and starting an interaction in TED.  In addition, TSC technicians will have the ability to access the workflow for handling customer requests for special notice options and other accommodations.  Modernization efforts will also include the replacement of older technology used to pass data from legacy systems.  In FY 2026, business workflow development efforts will focus on a streamlined process for assisting SSI recipients with updating address and telephone information, scheduling appointments and sending customers agency forms/links via their “my Social Security” account, text, or email.  In addition, the product will continue to work towards CHIP replacement by implementing the use of AI to develop high volume informational workflows such as Medicare, Social Security Statement etc.  Lastly, we are working to implement the first iteration of Customer Intake in TED in FY 2026.  This feature empowers technicians to seamlessly manage reception traffic and appointments for their office.  With streamlined check-in, identity verification, and task management capabilities, technicians can deliver faster, more accurate and personalized service without switching between multiple applications.  
-In March 2024, we expanded the Upload Documents and eSignature services, which allows beneficiaries and recipients to submit and sign documents electronically, to all field offices and workload support units nationwide.  We completed various</t>
-  </si>
-  <si>
     <t>Receiving Benefits from Other Sources, Military Status, Employment, Death, Citizenship, Age</t>
   </si>
   <si>
@@ -2285,22 +2225,6 @@
 We will continue our quality reviews and cost-effective program integrity work including medical continuing disability reviews and SSI non-medical redeterminations, to ensure individuals receive the payments for which they are eligible.
 For improper payments within the agency’s control, we will continue to invest in information technology modernization to provide our employees with user-friendly systems and tools to better service the public.  To meet the challenges of our growing workloads and provide the best service possible, we will streamline our policies and procedures and automate more of our business processes.  We will continue to issue periodic reminders and policy clarifications, as needed.
 We will increase our underpayment processing of our oldest and highest priority cases.  In addition, we updated our policy effective May 15, 2024 requiring that all underpayments of $15,000 or more requiring a peer review must be entered into the SSI Underpayment Case Control Log.  The SSI Underpayment Case Control Log application was created to provide stronger controls, consistency and facilitate accurate and timely processing of SSI underpayments.  As of September 30, 2025, we completed 98.12 percent of SSI underpayments that were identified as priority cases or pending for a year or more at the beginning of FY 2024.  Including cases where installments have been initiated but are awaiting the release of remaining installment payments, our completion percentage increases to 99.36 percent.</t>
-  </si>
-  <si>
-    <t>We developed the Improper Payment Alignment Strategy (IPAS) process to obtain agency-wide engagement and agreement on corrective actions to address the root causes of improper payments and the top deficiencies in our programs.  We have completed IPASs on multiple areas of Supplemental Security Income (SSI) improper payment deficiency, and we monitor the corrective actions within those IPASs.  Most of the corrective actions described within this response are from IPASs on financial accounts, wages, in-kind support and maintenance.  We also discuss broad-based efforts to ensure policy compliance and payment accuracy and ensure individuals receive the benefits they are due.  Beginning in September 2025, an SSI program lead will be overseeing the SSI process to review and consider potential proposals for SSI reform.  We will continue to examine and propose legislative and regulatory changes to simplify the administration of the SSI program.
-To ensure recipients remain eligible and receive the correct SSI payment amount, we conduct non-medical redeterminations (RZ).  RZs are a complete review of a recipient’s or couple’s non-medical eligibility factors (resources, income, and living arrangements).  To ensure the most cost-effective  investment of agency resources, we use a predictive model to estimate the likelihood and magnitude of overpayments to select cases for discretionary RZs.  Other cases are selected for RZs outside our modeling process based on selected case characteristics, such as manual deeming of income.  The RZ process also selects limited issue (LI) reviews, which are reviews of a specific issue or event related to a recipient’s or couple’s non-medical eligibility factors to determine whether the recipient or couple is still eligible for and receiving the correct SSI payment.  In FY 2025, we completed more than 2.4 million SSI nonmedical RZs and LIs.  In November 2024 and March 2025, we issued guidance to assist with achieving the FY 2025 LI and RZ workload goals, respectively.  We plan to process about 2.6 million RZs and LIs in FY 2026.
-We inform recipients and representative payees about their reporting responsibilities through various methods:  during interviews, with application and redetermination forms, in some award and post-eligibility notices, in check envelope enclosures, and in a booklet that accompanies award notices.  Our annual Cost of Living Adjustment notices include reminders about reporting changes that could affect payments and eligibility.  In FY 2025, we aired educational content on general SSI reporting responsibilities on televisions in field office reception areas.  Additionally, we have a National Change of Address (NCOA) contract and data exchange agreement with the U.S. Postal Service (USPS) for the Old-Age, Survivors, and Disability Insurance (OASDI) program.  We are electronically notified when an OASDI beneficiary reports an address change to the USPS and in most cases, the new address information automatically posts to our records.  If the beneficiary is concurrently entitled to SSI payments, their change of address does not automatically post to their SSI record as additional development is required to ensure payment accuracy.  In November 2024, we updated the NCOA change of address confirmation notice advising SSI recipients to contact the agency to report living arrangement changes that may have occurred.  Failure of recipients or their representative payees to timely and accurately report living arrangement changes can result in overpayments or underpayments.   
-Financial accounts that contribute to excess resources are a leading cause of SSI payment errors.  In field office reception areas, we will continue to display reminders on television to highlight the importance of reporting when account balances exceed the resource limit.  We use a tool, known as Access to Financial Institutions (AFI), to identify and verify financial account resources.  AFI verifies bank account information and detects undisclosed bank account balances with participating financial institutions and with the individual’s consent.  We use AFI for SSI initial claims, pre-effectuation review contacts, and RZs when SSI applicants/recipients allege total liquid resources of $400 or more.  When there is a resource-related diary present on an RZ or LI, we use AFI regardless of any liquid resource allegation.  In August 2025, we implemented a zero-dollar AFI tolerance for SSI 65+ aged claim allowances before adjudicating to payment.  In FY 2026, we intend to implement a zero-dollar AFI tolerance to all SSI initial claim allowances contingent upon updating the AFI contract and funding the additional volume of AFI requests.  This strategy mandates that AFI verification is fully completed prior to adjudication and before payments are issued, thereby eliminating improper payments at the source rather than pursuing recovery after the fact.  We will continue to explore expanding AFI usage in post entitlement situations and develop a systems enhancement to ensure that technicians run AFI in all instances required by policy.  
-An ABLE account is a special tax-advantaged savings account used by eligible individuals to pay for qualified disability expenses.  The account is owned by the person with the disability, and they must have become disabled before age 26.  Effective January 1, 2026, eligibility for ABLE accounts will expand to include individuals with a disability that began before age 46.  Proper reporting and accounting of ABLE accounts are essential to ensure exclusions are applied correctly and that SSI payments are accurate.  To influence understanding of ABLE accounts and encourage reporting of financial account information, in FY 2025, we aired educational content specific to reporting responsibilities and ABLE accounts on televisions in field office reception areas.  In March 2025, we also issued a reminder to technicians to avoid multiple postings of the same ABLE account and to ensure proper accounting of resources in ABLE accounts owned by recipients.  
-Recipients or their representative payees are required to report changes in their work activity and increases in earnings to ensure proper payments and continued eligibility for SSI payments.  Improper payments based on wages are a leading cause of improper payments in the SSI program; most occurring as a result of recipients or representative payees failing to report changes in work.  To reduce our reliance on recipient and representative payee reporting of employment and wage information, we published the Use of Electronic Payroll Data To Improve Program Administration final rule in December 2024.  Through the process known as the payroll information exchange (PIE), we obtain wage and employment information from a commercial payroll data provider for individuals who have provided authorization.  On April 7, 2025, we began the phased implementation of PIE with an initial exchange of 1 million Social Security numbers (SSN).  We gradually increased the exchanges each month until reaching full implementation of 10.7 million SSNs in September 2025.  We continued monthly exchanges with the full authorized population after September.  As part of the PIE implementation activities, we provided training to technicians, updated our policies and instructions, and released communication to the public.  In FY 2026 and beyond, we will implement measures to increase PIE authorizations; develop requirements for requesting historical wage data through PIE; develop a process for handling SSNs that are flagged for name mismatch and excluded from subsequent changes; streamline and improve notices, forms, and receipts related to PIE based on customer experience feedback; develop and implement enhanced management information; mismatch exclusions; and other enhancements.  PIE will improve payment accuracy, reduce improper payments, and reduce the reporting burden on individuals when they authorize us to obtain this information through an information exchange, and we receive it.  We also anticipate that implementation will result in more efficient use of our limited administrative resources because our technicians would reduce the amount of time they spend manually requesting this information from payroll data providers and employers; manually entering data into our systems from an individual’s pay records; contacting individuals; and assisting individuals with the results of incomplete or untimely reporting.
-For individuals or employers not participating in PIE, we continue to offer multiple reporting options such as the myWageReport (myWR) online tool, SSA Mobile Wage Reporting (SSAMWR), SSI Telephone Wage Reporting (SSITWR), by mail or in-office visit.  We also offer automated SSI wage reporting reminders for individuals who sign up to receive a monthly email or text message to report wages for the prior month.  From April-May 2025, we released social media posts on Facebook and X sharing a link to our YouTube video to help recipients learn why it is important to report wages and the automated electronic options for wage reporting.  This included instructional videos with step-by-step instructions on how to use the agency’s self-reporting wage applications.  In FY 2026, we continue to use our social media channels to post reminders for our recipients about the importance of promptly reporting changes that impact their eligibility and payment amounts.  These posts will inform recipients how we are required by law to adjust payments or recover debts when people receive payments they are not entitled to.  We will also continue to the send monthly email and text notification reminders to SSI recipients and deemors to report their wages timely.
-To improve understanding and reduce the burden on our customers and their employers, we are updating several disability-related forms.  In February 2025, we published a revised SSA-3033, Employee Work Questionnaire, and clarified policy and procedures for technicians developing subsidy for DI and SSI initial claims, and DI work continuing disability reviews.  The Office of Management and Budget (OMB) approved the SSA-821 Work Activity Report in July 2025, which we published in September 2025.  The revised SSA-820 Self-Employment Work Activity Report is currently pending OMB approval; we expect completion of the form in FY 2026.
-For certain improper payments outside of agency control, data or information needed does not exist because there is no database or dataset that currently exists where we can validate eligibility prior to making the payment.  For example, the law requires us to evaluate an individual’s income, which includes support and maintenance provided in-kind (or ISM).  This type of income is difficult to accurately value because it can fluctuate each month as household expenses, composition, and the type of assistance provided may change.  We rely on recipients to report changes in household expenses, composition, and contributions accurately and timely.  In FY 2025, we fully implemented three updates as part of SSI regulation simplification related to ISM.  These changes include: (1)  eliminating the requirement to provide detailed information about the value of food assistance received; (2) expanding the definition of a “public assistance household” by adding SNAP benefits to the list of public income-maintenance (PIM) programs and by requiring the receipt of a PIM payment for only one additional household member (other than the SSI applicant or recipient) instead of requiring the receipt of a PIM payment for every other member of the household; and (3) expanding the rental subsidy exception nationwide to simplify our ISM rules and ensure uniform application of the policy.  For item (2), a draft Notice of Proposed Rulemaking to rescind changes to the definition of a Public Assistance Household is pending review with the Office of Information and Regulatory Affairs.
-On August 1, 2025, we transitioned field office phone systems to the same telephone platform used by the teleservice centers.  By using the same telephone platform, we are able to route reports of SSI recipient change of address and living arrangement changes directly to a field office representative.  Field office representatives are able to update the SSI recipients’ record with the change of address and develop living arrangement or in-kind support and maintenance updates that could impact their payment amounts.  Previously, teleservice center representatives had to refer these reports to a field office for development at a later date and in some instances, the field office would have to recontact the claimant.  This prior business process could result in delays in processing the report and potentially create an improper payment.  
-We collect death data from a variety of sources and work to improve our death data processing so that we can effectively administer our programs.  We have a contract with every State Bureau of Vital Statistics (the custodians for death records) and with some jurisdictions to provide us death data.  Since 2002, we worked with States that want and are able to build a streamlined death registration process known as Electronic Death Registration (EDR).  As of July 2025, all 50 States, New York City, Washington, D.C., Puerto Rico, and the Commonwealth of the Northern Mariana Islands report deaths through the EDR process.  On September 30, 2024, we awarded a contract with the National Association for Public Health Statistics and Information Systems (NAPHSIS) on the acquisition of historical State death records.  In FY 2025, we worked with NAPHSIS on establishing the infrastructure required to receive the historical death data.  This multi-year effort will increase the accuracy, integrity, and completeness of our death data.  
-In March and June 2025, we updated Numident records with additional death information for non-beneficiary individuals that were over 120 years of age when there was no death record present on the Numident.  These efforts resulted in over 12 million death records being added to the Numident.  In March 2025, we also provided the Internal Revenue Service a one-time file concerning individuals listed in the agency’s enumeration system who are age 120 or older based on available information as recorded in that system.  Efforts are ongoing to update our Numident records for individuals over 100 years of age with death data.  We also increased the frequency with which the agency provides updates concerning the full file of death information to the Bureau of the Fiscal Service for use in the Do Not Pay system.? We implemented this change (from weekly to daily) on April 1, 2025.  In July 2025, we released a reminder to field office technicians to verify and record the death when a report of death on form DS-2060 U.S. Consular Report of Death Abroad is received. 
-For root causes where the data or information needed to process a payment correctly does not exist or the agency is unable to access the data or information needed, we are establishing alternate sources of information.  For example, we conducted 22 computer-matching agreements (CMA) with various Federal partners to help us determine eligibility and offset benefits for our programs.  The total annual savings attributed to these CMAs is approximately $14.9 billion, with an annual cost of approximately $510 million, yielding a positive benefit-to-cost ratio of about $29 to $1.  We plan to continue current CMAs that yield a positive cost-benefit ratio, expand effective CMAs to meet additional program needs, research current programs, work with internal stakeholders to identify data exchange needs, and pursue new data exchanges with potential partners.  In December 2024 and April 2025, we held Data Exchange Community of Practice meetings.  In FY 2026, we are working to reestablish the relationships with the current agency contacts, update the invitation list, and determine future topics for the meetings as resources allow. 
-In the Office of the Inspector General’s report on agency compliance with the Payment Integrity Information Act in FY 2024, they included a recommendation that the agency complete the Foreign Travel Data (FTD) project.  FTD is an agency application with direct access to the Departmen</t>
   </si>
   <si>
     <t>Residency, Receiving Benefits from Other Sources, Prisoner Status, Military Status, Marital Status, Financial, Employment, Death, Address/location</t>
@@ -3619,6 +3543,103 @@
   <si>
     <t>Program Code</t>
   </si>
+  <si>
+    <t>The agency has many of the essential components needed to reduce improper payments and unknown payments. While HUD made remarkable strides in fiscal year (FY) 2025, significant issues still remain and enhancements in human capital, information systems, and infrastructure are needed to continue to improve payment integrity. HUD launched Project Voucher, a whole-of-agency transformation effort to improve the integrity and efficiency of its rental assistance programs. The initiative aims to eliminate fraud, waste, and abuse, maximize resources, and ensure responsible stewardship of taxpayer dollars, while establishing greater visibility and traceability in rental assistance payments. This initiative would enable improved collection, management, and assessment of critical tenant eligibility information and documentation, such as proof of identify, housing, income, assets, applicable income deductions, and complete HUD forms for applicable participants. HUD is also conducting a study to confirm that its programs are using taxpayer dollars for the correct purpose. The study includes gathering data and information that links the impact of the taxpayer dollars spent for each program to the outcomes for people who benefit from HUD's programs related to affordable housing, poverty, and other measures. Together, these projects will aim to further reveal the additional internal controls, human capital, information systems, and other policy and infrastructure needs required to reduce improper and unknown payments. By strengthening these areas, the agency aims to achieve a level of reduction in unknown payments that justifies the associated expenditures. This approach ensures that the cost of implementing further controls do not exceed the savings gained from preventing or recovering improper payments. These projects represent a significant commitment to enhancing program integrity, preventing future payment errors, and ensuring federal funds are allocated to U.S. citizens and eligible non-citizens.</t>
+  </si>
+  <si>
+    <t>The agency has many of the essential components needed to reduce improper payments and unknown payments. While HUD made remarkable strides in fiscal year (FY) 2025, significant issues still remain and enhancements in human capital, information systems, and infrastructure are needed to continue to improve payment integrity. HUD launched Project Voucher, a whole-of-agency transformation effort to improve the integrity and efficiency of its rental assistance programs. The initiative aims to eliminate fraud, waste, and abuse, maximize resources, and ensure responsible stewardship of taxpayer dollars, while establishing greater visibility and traceability in rental assistance payments. This initiative would enable improved collection, management, and assessment of critical tenant eligibility information and documentation, such as proof of identify, housing, income, assets, applicable income deductions, and complete HUD forms for applicable participants. HUD is also conducting a study to confirm that its programs are using taxpayer dollars for the correct purpose. The study includes gathering data and information that links the impact of the taxpayer dollars spent for each program to the outcomes for people who benefit from HUD's programs related to affordable housing, poverty, and other measures. Together, these projects will aim to further reveal the additional internal controls, human capital, information systems, and other policy and infrastructure needs required to reduce improper and unknown payments. 
+By strengthening these areas, the agency aims to achieve a level of reduction in unknown payments that justifies the associated expenditures. This approach ensures that the cost of implementing further controls do not exceed the savings gained from preventing or recovering improper payments. These projects represent a significant commitment to enhancing program integrity, preventing future payment errors, and ensuring federal funds are allocated to U.S. citizens and eligible non-citizens.</t>
+  </si>
+  <si>
+    <t>To address the causes of unknown payments and prevent future unknown payments, a series of corrective actions have been taken and planned for fiscal year (FY) 2026. In FY 2025 HUD introduced innovative methods and advanced analytics to evaluate tenant and recipient records. This approach allowed HUD to analyze millions of payment records from FY 2024, rather than relying on traditional sampling of just a few hundred records. As a result, HUD gained greater insights into potential risks and issues while identifying problematic records and estimating payments errors. This analytical strategy enables HUD to detect eligibility and payment errors more effectively as well as address the disbursement of funding design and complex eligibility and program requirements, which increases the risk of payment errors. For the first time, HUD evaluated all tenant records across the rental assistance programs, uncovering eligibility issue totaling billions in unknown Tenant-Based Rental Assistance (TBRA) payments. HUD immediately took action to remediate these findings. During FY 2025 the Office of Public and Indian Housing (PIH) strengthened controls with pre-award verifications to improve SAM.gov registration status, ensuring that funds were not paid to ineligible entities. HUD also reestablished its Computer Matching Agreement with the Department of the Treasury as of May 1, 2025, and is working to enable near-real-time eligibility verification through the Treasury Do Not Pay verification portal. HUD already realized the benefits of Treasury’s Do Not Pay databases, referencing the databases to flag over $69 million in payments made on behalf of deceased tenants in FY 2024 under the TBRA program. Further, PIH is actively investigating the approximately $1.5 billion of unknown payments to take corrective action and prevent further issues. This year, HUD conducted its first collaboration with the Department of Homeland Security to identify potential ineligible non-citizens receiving rental assistance in the Section 8 and Section 9 portfolio, including the Operating Fund, TBRA and PBRA programs. A total of 8.8 million tenant records were analyzed, confirming U.S. citizenship and non-citizen eligibility for 8.6 million citizen and non-citizen eligible tenants. The analysis of the records indicates that thousands of ineligible non-citizens are potentially receiving assistance under the programs. The OCFO established the Strike Force to enhance efforts in eliminating fraud, corruption, and immigration violations within Public Housing Agencies (PHAs) as mandated by new regulations. To fulfill these mandates, the Strike Force utilizes publicly available information, compiles data from across HUD and identifies potential risk factors associated with PHAs and their personnel. This analysis enables the team to compile detailed, preliminary risk assessments and intelligence reports and present them to the appropriate law enforcement agency, expediting the detection and resolution of possible misconduct. HUD also launched Project Voucher, a whole-of-agency transformation effort to improve the integrity and efficiency of its rental assistance programs. The initiative aims to eliminate fraud, waste, and abuse, maximize resources, and ensure responsible stewardship of taxpayer dollars, while establishing greater visibility and traceability in rental assistance payments. Additionally, HUD is conducting a study to confirm that its programs are using taxpayer dollars for the correct purpose. The study includes gathering data and information that links the impact of the taxpayer dollars spent for each program to the outcomes for people who benefit from HUD's programs related to affordable housing, poverty, and other measures. HUD's comprehensive reviews, Project Voucher, and research efforts represent a significant commitment to enhance program integrity, prevent future payment errors, and ensure federal funds are allocated to those who genuinely need assistance. In FY 2026, HUD plans to continue the progress made in FY 2025. By increasing its use of automation tools designed to identify SAM.gov registrations expired or soon to be expired, prior to processing payments, HUD aims to further reduce the risk of payments being made to ineligible entities. Additionally, performing near-real-time eligibility verification through the Treasury Do Not Pay verification portal will enhance HUD’s ability to reduce fraud and prevent improper payments. With Project Voucher and research efforts, HUD is paving the way for a more accountable and transparent rental assistance system. Further, Strike Force investigations will aim to reveal opportunities for greater accountability across PHAs. Ultimately, the greater visibility into the unknown payments has enabled HUD to begin to design technology, process, and policy improvements that will strengthen its payment integrity programs in the long-run.</t>
+  </si>
+  <si>
+    <t>We developed the Improper Payment Alignment Strategy (IPAS) process to obtain agency-wide engagement and agreement on corrective actions to address the root causes of improper payments and the top deficiencies in our programs. We have completed IPASs on multiple areas of Disability Insurance (DI) improper payment deficiency, and we monitor the corrective actions within those IPASs. Most of the corrective actions described within this response are from two new IPASs we completed in FY 2025 (computations and relationship/dependency) as well as IPASs on substantial gainful activity (SGA), windfall elimination provision (WEP) and government pension offset (GPO), and improving death data processes. We also discuss broad-based efforts to ensure policy compliance and payment accuracy and ensure individuals receive the benefits they are due.
+SGA is the performance of significant physical or mental activities in work for pay or profit, or in work of a type generally performed for pay or profit, regardless of the legality of the work. Beneficiaries are required to report changes in their work activity and increases in earnings to ensure proper payments and continued eligibility for benefits. Improper payments based on SGA are a leading cause of improper payments in the OASDI program; most occurring as a result of beneficiaries or representative payees failing to report changes in work.
+To reduce our reliance on beneficiary and representative payee reporting of employment and wage information, we published the Use of Electronic Payroll Data To Improve Program Administration final rule in December 2024. Through the process known as the payroll information exchange (PIE), we obtain wage and employment information from a commercial payroll data provider for individuals who have provided authorization. On April 7, 2025, we began the phased implementation of PIE with an initial exchange of 1 million Social Security numbers (SSN). We gradually increased the exchanges each month until reaching full implementation of 10.7 million SSNs in September 2025. We continued monthly exchanges with the full authorized population after September. As part of the PIE implementation activities, we provided training to technicians, updated our policies and instructions, and released communication to the public. In FY 2026 and beyond, we will implement measures to increase PIE authorizations; develop requirements for requesting historical wage data through PIE; develop a process for handling SSNs that are flagged for name mismatch and excluded from subsequent changes; streamline and improve notices, forms, and receipts related to PIE based on customer experience feedback; develop and implement enhanced management information; mismatch exclusions; and other enhancements. PIE will improve payment accuracy, reduce improper payments, and reduce the reporting burden on individuals when they authorize us to obtain this information through an information exchange, and we receive it. We also anticipate that implementation will result in more efficient use of our limited administrative resources because our technicians would reduce the amount of time they spend manually requesting this information from payroll data providers and employers; manually entering data into our systems from an individual’s pay records; contacting individuals; and assisting individuals with the results of incomplete or untimely reporting.
+For individuals or employers not participating in PIE, we continue to offer electronic wage reporting tools, such as the myWageReport (myWR) online tool. myWR allows Disability Insurance beneficiaries, Supplemental Security Income (SSI) recipients, concurrent beneficiaries, and representative payees to report wages and view, print, or save a receipt. Self-reporters and their representative payees can report wages that occurred within a two-year timeframe from the reporting date. From April-May 2025, we released social media posts on Facebook and X sharing a link to our YouTube video to help beneficiaries learn why it is important to report wages and the automated electronic options for wage reporting. This included instructional videos with step-by-step instructions on how to use the agency’s self-reporting wage applications. In FY 2026, we will continue to use our social media channels to post reminders for our beneficiaries about the importance of promptly reporting changes that impact their eligibility and payment amounts. These posts will inform beneficiaries how we are required by law to adjust payments or recover debts when people receive payments they are not entitled to.
+In July 2025, we started a national Targeted Work Review Process (TWRP) for specific work continuing disability reviews (CDR). The TWRP leverages the expertise of a cadre of technicians to use readily available earnings data to formulate a proposed work CDR decision prior to requesting work activity report. Technicians will send both the work activity report and due process notice simultaneously. The TWRP aims to reduce work CDR processing time by allowing one technician to process the case from start to finish and reducing delays in sending/receiving evidence. TWRP continued into early FY 2026, and we plan to evaluate its outcomes later in FY 2026. We are also developing a new Electronic Work Continuing Disability Review (eWCDR) application to replace and modernize the system technicians use to process CDRs based on work activity. The new system will enforce policy and best practices with an intuitive user interface and will eliminate current system limitations that lead to large improper payments through delays and processing errors. The application will streamline the disability review process and will have a positive impact in reducing substantial gainful activity improper payments. In FY 2025, efforts continued to develop eWCDR capabilities that allow technicians to receive beneficiaries’ reports of work, document and evaluate pay stubs and self-employment income, mail out forms and notices, and collect Management Information. We plan to release the minimum viable product to technicians by the end of FY 2026. We also use WorkSmart, a tool that helps identify DI beneficiaries whose earnings may place them at risk of overpayment. WorkSmart continues to alert cases for work CDRs based on available earnings data. In addition, with the appropriate authorization, WorkSmart will utilize PIE data to identify and alert cases that may require a work CDR.
+We complete Work CDR Quality Reviews to ensure compliance with policy and the Bipartisan Budget Act (BBA) of 2015 by evaluating a monthly, stratified random sample of processed Work CDRs. This review captures processing times, assesses Trust Fund impact from policy non-compliance, measures accuracy rates, identifies procedural and training improvements, and collects data on new processing procedures. We provide case-level feedback and share the broader data analysis with stakeholders. We completed data analysis of FY 2023 and FY 2024 reviews and plan to publish them in FY 2026. We are planning the FY 2026 review to evaluate Work CDR accuracy amid the implementation of PIE and other procedural changes.
+To improve understanding and reduce the burden on our customers and their employers, we are updating several disability-related forms. In February 2025, we published a revised SSA-3033, Employee Work Questionnaire, and clarified policy and procedures for technicians developing subsidy for DI and SSI initial claims, and DI work continuing disability reviews. The Office of Management and Budget (OMB) approved the SSA-821 Work Activity Report in July 2025, which we published in September 2025. The revised SSA-820 Self-Employment Work Activity Report is currently pending OMB approval; we expect completion of the form in FY 2026.
+WEP and GPO reduced or offset Social Security monthly benefits to beneficiaries who received a pension based on non-covered earnings. Most of these workers had non-covered earnings from federal, state, or local governments. Errors relating to WEP/GPO have been one of the leading causes of OASI improper payments. We had previously relied on applicants, beneficiaries, or their representative payees to report their entitlement to current or future non-covered pensions; however, they did not always report the receipt of or changes to a pension, resulting in benefit calculation and payment errors. WEP and GPO errors also occurred when the agency did not correctly impose reductions or offset, misapplied exceptions or exemptions, or applied WEP but not GPO (or vice versa) for dually entitled beneficiaries.
+We developed a comprehensive corrective action plan to address multiple underlying causes of WEP/GPO improper payments. We assessed the root causes of improper payments based on these changes and developed policy, data, systems, and training solutions in line with each of the root causes of improper payments. On January 5, 2025, the Social Security Fairness Act of 2023 was signed into law, thereby repealing WEP/GPO. December 2023 is the last month that WEP and GPO will apply. This means that those rules no longer apply to benefits payable for January 2024 and later. The agency worked quickly and successfully to implement these changes. As of July 7, 2025, we completed sending over 3.1 million payments, totaling $17 billion, to beneficiaries eligible under the Social Security Fairness Act. The average retroactive payment was $7,208. As of September 30, 2025, we have taken over 387,000 new initial claims. We began releasing higher monthly benefit payments in April 2025. We anticipate the WEP/GPO repeal will significantly reduce and eventually eliminate WEP/GPO improper payments in future years.
+Computational errors occur due to many factors. Generally, these factors include: systems limitations for complex cases; manual calculation of benefits involving complicated policies; technician errors; incorrect earnings postings; beneficiaries not reporting complete and pertinent information; and lack of accurate and accessible data. We developed processes using UIPath software to create automated “robotic” programs that perform routine or repetitive tasks and increase the speed and accuracy of manual processing. Robotic Processing Automation (RPA), or “BOTs,” are available to Processing Center (PC) technicians to assist with processing manual awards or post-entitlement actions. Since January 2021, seven PC-specific BOTs have been created to assist with DI and Old-Age and Survivors actions and placed into production. In December 2024, we provided general reminders and guidance for PC technicians on BOT usage. We completed the final testing stages of the UiPath Assistant software and rolled out the new platform to PC users in August 2025. We are making a long-term investment in robotics technology using the software to improve business processes and eliminate manual actions.
+In January 2025, we released instructions to field office technicians to review earning records for identified pending retirement and disability claims. Validating earnings records associated with pending claims ensures accurate eligibility and payment amounts. In April 2025, we released a reminder to frontline technicians including information on reducing improper payments related to benefit computations. When automated systems cannot compute benefit amounts in certain situations, there are a variety of computations tools that technicians should use to ensure accuracy. In May 2025, we updated policy instructions associated with temporary and ongoing earnings inaccuracies and coding used to trigger an alert for technicians to review and ensure the accuracy of earnings records and Primary Insurance Amounts before automatic benefit increases. In the May 2025 policy update, we expanded the coding to include “all disclaimed wages and those institutionalized.” This action stemmed from an Office of the Inspector General report on institutionalized beneficiaries who have earnings.
+The Federal Employee Compensation Act (FECA) provides income and medical cost protection to covered Federal civilian employees injured on the job, employees who have incurred a work-related injury or occupational disease and beneficiaries of employees whose death is attributable to a job-related injury or occupational disease. FECA is administered by the Department of Labor (DOL), and receipt of FECA benefits can offset DI benefits. In December 2023, we established a Memorandum of Understanding with DOL for use of an employee compensation portal. Technicians can submit individual real-time queries in the portal to obtain FECA data and complete computations. We continue to explore data exchange opportunities that would improve efficiency and accuracy of related computations by eliminating the need for a manual query and transition to a batch process. We are working to complete the computer matching agreement and will begin implementation of the data exchange in FY 2026 should funding be available.
+Marital status and child relationship factors are material when determining entitlement to certain auxiliary and survivor benefits. Improper payments occur due to beneficiaries failing to report changes in marital status, the agency’s inability to automate, and difficulty expanding data exchanges to include the exchange of marital information. To address these issues, in FY 2025, we have been airing relationship and dependency reminders on televisions in field office reception areas. In April 2025, we released a reminder to frontline technicians on checking for program entitlement when an individual changes their name due to marriage or divorce. The guidance also included a reminder on verifying that all child-in-care information is entered in the system correctly. In FY 2026, if resources allow, we will explore options to expand the Internet Social Security Number Replacement’s current process and incorporate downstream application alerts to reduce instances of improper payments.
+We collect death data from a variety of sources and work to improve our death data processing so that we can effectively administer our programs. We have a contract with every State Bureau of Vital Statistics (the custodians for death records) and with some jurisdictions to provide us death data. Since 2002, we worked with States that want and are able to build a streamlined death registration process known as Electronic Death Registration (EDR). As of July 2025, all 50 States, New York City, Washington, D.C., Puerto Rico, and the Commonwealth of the Northern Mariana Islands report deaths through the EDR process. On September 30, 2024, we awarded a contract with the National Association for Public Health Statistics and Information Systems (NAPHSIS) on the acquisition of historical State death records. In FY 2025, we worked with NAPHSIS on establishing the infrastructure required to receive the historical death data. This multi-year effort will increase the accuracy, integrity, and completeness of our death data.
+In March and June 2025, we updated Numident records with additional death information for non-beneficiary individuals that were over 120 years of age when there was no death record present on the Numident. These efforts resulted in over 12 million death records being added to the Numident. In March 2025, we also provided the Internal Revenue Service a one-time file concerning individuals listed in the agency’s enumeration system who are age 120 or older based on available information as recorded in that system. Efforts are ongoing to update our Numident records for individuals over 100 years of age with death data. We also increased the frequency with which the agency provides updates concerning the full file of death information to the Bureau of the Fiscal Service for use in the Do Not Pay system.? We implemented this change (from weekly to daily) on April 1, 2025. In July 2025, we released a reminder to field office technicians to verify and record the death when a report of death on form DS-2060 U.S. Consular Report of Death Abroad is received.
+For root causes where the data or information needed to process a payment correctly does not exist or the agency is unable to access the data or information needed, we are establishing alternate sources of information. For example, we conducted 22 computer-matching agreements (CMA) with various Federal partners to help us determine eligibility and offset benefits for our programs. The total annual savings attributed to these CMAs is approximately $14.9 billion, with an annual cost of approximately $510 million, yielding a positive benefit-to-cost ratio of about $29 to $1. We plan to continue current CMAs that yield a positive cost-benefit ratio, expand effective CMAs to meet additional program needs, research current programs, work with internal stakeholders to identify data exchange needs, and pursue new data exchanges with potential partners. In December 2024 and April 2025, we held Data Exchange Community of Practice meetings. In FY 2026, we are working to reestablish the relationships with the current agency contacts, update the invitation list, and determine future topics for the meetings as resources allow.
+We have several broad-based initiatives in place or underway that are designed to ensure technician compliance with policy and improve payment accuracy.
+We complete Transaction Accuracy Reviews (TAR) on a triennial basis to assist in assessing operational quality. TAR focuses on a review of the nonmedical factors of entitlement and eligibility for OASI and DI payments in initial claims awards and disallowances. TAR findings provide insight to causes of improper payments and identify recommendations for improvement, which are shared with agency stakeholders. TAR is completed on a triennial basis. We will complete the next TAR report in FY 2027 based on reviews of FY 2026 case samples.
+In September 2024, we released the 21st Century PolicyNet (21CPN), which replaced PolicyNet, the 20+ year-old software platform that contains multiple applications and hosts tens of thousands of pages of policy instruction. The overall goals of 21CPN are an improved user experience, process efficiencies for the author, publisher, and researcher role, as well as improving searching capabilities, including the use of intelligent search. In December 2024, we launched improvements that introduced new message types, enhanced search functionalities, upgraded navigation features, included spell check for technician searches, and provided access to a variety of operational resources, archives, and margin notes. In April 2025, we successfully finished the data migration process and implemented enhanced search features. These improvements now encompass the hearings, appeal, and litigation law manual, as well as Social Security rulings and acquiescence rulings, along with policy documents and ownership details. Additionally, we provided quick access to agency form repositories and included a user guide for 21CPN. In June 2025, we launched an advanced search feature designed to improve the accessibility of policies, procedures, and instructions. Additionally, we upgraded the application's presentation and usability by incorporating a series of content clusters and a "Trending" topics section to showcase and highlight agency initiatives for key stakeholders. In September 2025, we broadened the data set to incorporate various procedural content clusters, link libraries, question and answer sections, and related instructions links. Furthermore, we improved the presentation functionality by introducing subscriptions and daily messages. Finally, by the end of FY 2026, contingent upon successful testing and evaluation, we plan to launch a generative AI "Policy Assistant Tool (PAT)" designed to simplify the search process for policies, procedures, and instructions. This tool will assist technicians in quickly and accurately finding and understanding relevant information to aid in decision-making.
+We developed the Technician Experience Dashboard (TED) as an enterprise customer relationship management solution that will provide a single location for information about our customers’ interactions with the agency to make it easier for our employees to help the public and increases efficiency and accuracy, improving the overall customer experience. In February 2024, we rolled TED out nationally to all field offices (FO) and workload support units. In November 2024, we expanded TED to all teleservice (TSC) centers. TED modernized the previous 30-year-old Customer Help and Information Program (CHIP) that assisted TSC technicians when responding to customer inquiries via telephone. In January and March 2025, we released two iterations of TED enhancements, improving upon the functionality for field office and teleservice centers. In April and June 2025, we enhanced the identity verifications procedures within TED to send a Security Authentication Personal Identification Number to authenticated customers (that technicians subsequently verify) before making direct deposit and direct express enrollments, changes, or cancellations over the phone.
+In December 2025, we will release a workflow in TED that allows FO and TSC technicians to update payment information for Supplemental Security Income (SSI) recipients. The release will also include the FO expansion of the ability to automate the process for collecting the customer SSN and starting an interaction in TED. In addition, TSC technicians will have the ability to access the workflow for handling customer requests for special notice options and other accommodations. Modernization efforts will also include the replacement of older technology used to pass data from legacy systems. In FY 2026, business workflow development efforts will focus on a streamlined process for assisting SSI recipients with updating address and telephone information, scheduling appointments and sending customers agency forms/links via their “my Social Security” account, text, or email. In addition, the product will continue to work towards CHIP replacement by implementing the use of artificial intelligence to develop high volume informational workflows such as Medicare, Social Security Statement etc. Lastly, we are working to implement the first iteration of Customer Intake in TED in FY 2026. This feature empowers technicians to seamlessly manage reception traffic and appointments for their office. With streamlined check-in, identity verification, and task management capabilities, technicians can deliver faster, more accurate and personalized service without switching between multiple applications.
+In March 2024, we expanded the Upload Documents and eSignature services, which allows beneficiaries and recipients to submit and sign documents electronically, to all field offices and workload support units nationwide. We completed various enhancements and expanded available forms throughout FYs 2024 and 2025. Beginning March 29, 2025, a new customer-initiated option is available allowing customers to electronically submit certain forms to the agency without technician initiation. This self-service approach empowers customers to initiate document uploads as soon as they recognize a need, eliminating delays caused by waiting for technician outreach. In FY 2026, we will continue to webify forms for a mobile friendly experience and increase the number of forms. We plan to expand customer-initiated submissions to allow individual representative payees to submit documents.
+To improve accuracy of processing overpayment actions, from July 2024 to September 2025, we conducted in-line quality reviews of almost 4,300 high-dollar overpayments exceeding $50,000. From September 2024 to September 2025, we conducted post adjudicative reviews of almost 9,400 overpayments exceeding $10,000. We make corrections to identified errors and use the analysis and findings to conduct training and issues reminders to processing center (PC) technicians. Additionally, in October 2024, we conducted a probe of recently processed overpayments to obtain a baseline accuracy, inform a further in-depth study, determine specific causes of overpayment errors, whether technicians and automated systems had difficulty processing one type of overpayment as compared to another, and to see the effects of changes made to the overpayment process based on prior quality reviews (e.g., requiring a second review for overpayments posted to a record in excess of $50,000). Based on the results of the probe, in May 2025, we began conducting a quality review of recently processed overpayments stratified by PC and providing case level feedback to the PCs. In spring 2026, we plan to provide overall accuracy findings to each PC, along with information on the errors identified, and recommendations for improvement. We are considering further reviews in FY 2026, dependent upon FY 2025 findings, available resources, and competing priorities.
+We provided resources for technicians to use when reviewing and processing requests for waiver of an overpayment. In February 2025, within an existing waiver processing toolkit, we added links to live waiver training sessions and an updated overpayment waiver decision tree. In June 2025, we created the updated SSA-632-BK, Request for Waiver of Overpayment Recovery, to streamline the process for submitting overpayment waiver requests and improve ease of use for the public.
+In FY 2024, we published the revised Notice Language Clearance Process policy, which incorporates review and approval of notice language through the plain language and the customer experience lens. In FY 2025, we used this new policy to provide a plain language review of 22 notices.
+For the root cause of overpayments due to our failure to access data or information needed (approximately $927.2 million), our corrective actions and strategies fall within several high-level categories such as automation, training, and cross enterprise sharing. For overpayments outside of the agency’s control (approximately $905.2 million), we are addressing the challenge of reliance on self-reporting by promoting timely wage reporting and issuing reminders on reporting responsibilities. We also began utilizing an automated information exchange with a commercial payroll data provider to reduce the reliance on self-reporting of wages; this exchange is referred to as the Payroll Information Exchange.
+We monitor the status of improper payment corrective actions through recurring stakeholder and senior executive meetings. We evaluated existing initiatives and developed a comprehensive approach to identify, support, and prioritize new and planned reduction initiatives that target the root causes of leading causes of improper payments. The purpose of this effort is to strategically align agency wide initiatives that will have the most significant impact to the detection and prevention of improper payments. By identifying and analyzing the root causes of the improper payments, we channel our efforts in the most efficient manner ensuring that we are fiscally responsible as we implement a corrective action plan.
+We will continue to find opportunities to explore cost-effective corrective action plans based on our evaluations. However, we continue to note that the complexity of our Disability Insurance program makes it extremely difficult to determine the dollar value associated with a particular corrective action.</t>
+  </si>
+  <si>
+    <t>We developed the Improper Payment Alignment Strategy (IPAS) process to obtain agency-wide engagement and agreement on corrective actions to address the root causes of improper payments and the top deficiencies in our programs. We have completed IPASs on multiple areas of Supplemental Security Income (SSI) improper payment deficiency, and we monitor the corrective actions within those IPASs. Most of the corrective actions described within this response are from IPASs on financial accounts, wages, in-kind support and maintenance. We also discuss broad-based efforts to ensure policy compliance and payment accuracy and ensure individuals receive the benefits they are due. Beginning in September 2025, an SSI program lead will be overseeing the SSI process to review and consider potential proposals for SSI reform. We will continue to examine and propose legislative and regulatory changes to simplify the administration of the SSI program.
+To ensure recipients remain eligible and receive the correct SSI payment amount, we conduct non-medical redeterminations (RZ). RZs are a complete review of a recipient’s or couple’s non-medical eligibility factors (resources, income, and living arrangements). To ensure the most cost-effective investment of agency resources, we use a predictive model to estimate the likelihood and magnitude of overpayments to select cases for discretionary RZs. Other cases are selected for RZs outside our modeling process based on selected case characteristics, such as manual deeming of income. The RZ process also selects limited issue (LI) reviews, which are reviews of a specific issue or event related to a recipient’s or couple’s non-medical eligibility factors to determine whether the recipient or couple is still eligible for and receiving the correct SSI payment. In FY 2025, we completed more than 2.4 million SSI nonmedical RZs and LIs. In November 2024 and March 2025, we issued guidance to assist with achieving the FY 2025 LI and RZ workload goals, respectively. We plan to process about 2.6 million RZs and LIs in FY 2026.
+We inform recipients and representative payees about their reporting responsibilities through various methods: during interviews, with application and redetermination forms, in some award and post-eligibility notices, in check envelope enclosures, and in a booklet that accompanies award notices. Our annual Cost of Living Adjustment notices include reminders about reporting changes that could affect payments and eligibility. In FY 2025, we aired educational content on general SSI reporting responsibilities on televisions in field office reception areas. Additionally, we have a National Change of Address (NCOA) contract and data exchange agreement with the U.S. Postal Service (USPS) for the Old-Age, Survivors, and Disability Insurance (OASDI) program. We are electronically notified when an OASDI beneficiary reports an address change to the USPS and in most cases, the new address information automatically posts to our records. If the beneficiary is concurrently entitled to SSI payments, their change of address does not automatically post to their SSI record as additional development is required to ensure payment accuracy. In November 2024, we updated the NCOA change of address confirmation notice advising SSI recipients to contact the agency to report living arrangement changes that may have occurred. Failure of recipients or their representative payees to timely and accurately report living arrangement changes can result in overpayments or underpayments.
+Financial accounts that contribute to excess resources are a leading cause of SSI payment errors. In field office reception areas, we will continue to display reminders on television to highlight the importance of reporting when account balances exceed the resource limit. We use a tool, known as Access to Financial Institutions (AFI), to identify and verify financial account resources. AFI verifies bank account information and detects undisclosed bank account balances with participating financial institutions and with the individual’s consent. We use AFI for SSI initial claims, pre-effectuation review contacts, and RZs when SSI applicants/recipients allege total liquid resources of $400 or more. When there is a resource-related diary present on an RZ or LI, we use AFI regardless of any liquid resource allegation. In August 2025, we implemented a zero-dollar AFI tolerance for SSI 65+ aged claim allowances before adjudicating to payment. In FY 2026, we intend to implement a zero-dollar AFI tolerance to all SSI initial claim allowances contingent upon updating the AFI contract and funding the additional volume of AFI requests. This strategy mandates that AFI verification is fully completed prior to adjudication and before payments are issued, thereby eliminating improper payments at the source rather than pursuing recovery after the fact. We will continue to explore expanding AFI usage in post entitlement situations and develop a systems enhancement to ensure that technicians run AFI in all instances required by policy.
+An ABLE account is a special tax-advantaged savings account used by eligible individuals to pay for qualified disability expenses. The account is owned by the person with the disability, and they must have become disabled before age 26. Effective January 1, 2026, eligibility for ABLE accounts will expand to include individuals with a disability that began before age 46. Proper reporting and accounting of ABLE accounts are essential to ensure exclusions are applied correctly and that SSI payments are accurate. To influence understanding of ABLE accounts and encourage reporting of financial account information, in FY 2025, we aired educational content specific to reporting responsibilities and ABLE accounts on televisions in field office reception areas. In March 2025, we also issued a reminder to technicians to avoid multiple postings of the same ABLE account and to ensure proper accounting of resources in ABLE accounts owned by recipients.
+Recipients or their representative payees are required to report changes in their work activity and increases in earnings to ensure proper payments and continued eligibility for SSI payments. Improper payments based on wages are a leading cause of improper payments in the SSI program; most occurring as a result of recipients or representative payees failing to report changes in work. To reduce our reliance on recipient and representative payee reporting of employment and wage information, we published the Use of Electronic Payroll Data To Improve Program Administration final rule in December 2024. Through the process known as the payroll information exchange (PIE), we obtain wage and employment information from a commercial payroll data provider for individuals who have provided authorization. On April 7, 2025, we began the phased implementation of PIE with an initial exchange of 1 million Social Security numbers (SSN). We gradually increased the exchanges each month until reaching full implementation of 10.7 million SSNs in September 2025. We continued monthly exchanges with the full authorized population after September. As part of the PIE implementation activities, we provided training to technicians, updated our policies and instructions, and released communication to the public. In FY 2026 and beyond, we will implement measures to increase PIE authorizations; develop requirements for requesting historical wage data through PIE; develop a process for handling SSNs that are flagged for name mismatch and excluded from subsequent changes; streamline and improve notices, forms, and receipts related to PIE based on customer experience feedback; develop and implement enhanced management information; mismatch exclusions; and other enhancements. PIE will improve payment accuracy, reduce improper payments, and reduce the reporting burden on individuals when they authorize us to obtain this information through an information exchange, and we receive it. We also anticipate that implementation will result in more efficient use of our limited administrative resources because our technicians would reduce the amount of time they spend manually requesting this information from payroll data providers and employers; manually entering data into our systems from an individual’s pay records; contacting individuals; and assisting individuals with the results of incomplete or untimely reporting.
+For individuals or employers not participating in PIE, we continue to offer multiple reporting options such as the myWageReport (myWR) online tool, SSA Mobile Wage Reporting (SSAMWR), SSI Telephone Wage Reporting (SSITWR), by mail or in-office visit. We also offer automated SSI wage reporting reminders for individuals who sign up to receive a monthly email or text message to report wages for the prior month. From April-May 2025, we released social media posts on Facebook and X sharing a link to our YouTube video to help recipients learn why it is important to report wages and the automated electronic options for wage reporting. This included instructional videos with step-by-step instructions on how to use the agency’s self-reporting wage applications. In FY 2026, we continue to use our social media channels to post reminders for our recipients about the importance of promptly reporting changes that impact their eligibility and payment amounts. These posts will inform recipients how we are required by law to adjust payments or recover debts when people receive payments they are not entitled to. We will also continue to the send monthly email and text notification reminders to SSI recipients and deemors to report their wages timely.
+To improve understanding and reduce the burden on our customers and their employers, we are updating several disability-related forms. In February 2025, we published a revised SSA-3033, Employee Work Questionnaire, and clarified policy and procedures for technicians developing subsidy for DI and SSI initial claims, and DI work continuing disability reviews. The Office of Management and Budget (OMB) approved the SSA-821 Work Activity Report in July 2025, which we published in September 2025. The revised SSA-820 Self-Employment Work Activity Report is currently pending OMB approval; we expect completion of the form in FY 2026.
+For certain improper payments outside of agency control, data or information needed does not exist because there is no database or dataset that currently exists where we can validate eligibility prior to making the payment. For example, the law requires us to evaluate an individual’s income, which includes support and maintenance provided in-kind (or ISM). This type of income is difficult to accurately value because it can fluctuate each month as household expenses, composition, and the type of assistance provided may change. We rely on recipients to report changes in household expenses, composition, and contributions accurately and timely. In FY 2025, we fully implemented three updates as part of SSI regulation simplification related to ISM. These changes include: (1) eliminating the requirement to provide detailed information about the value of food assistance received; (2) expanding the definition of a “public assistance household” by adding SNAP benefits to the list of public income-maintenance (PIM) programs and by requiring the receipt of a PIM payment for only one additional household member (other than the SSI applicant or recipient) instead of requiring the receipt of a PIM payment for every other member of the household; and (3) expanding the rental subsidy exception nationwide to simplify our ISM rules and ensure uniform application of the policy. For item (2), a draft Notice of Proposed Rulemaking to rescind changes to the definition of a Public Assistance Household is pending review with the Office of Information and Regulatory Affairs.
+On August 1, 2025, we transitioned field office phone systems to the same telephone platform used by the teleservice centers. By using the same telephone platform, we are able to route reports of SSI recipient change of address and living arrangement changes directly to a field office representative. Field office representatives are able to update the SSI recipients’ record with the change of address and develop living arrangement or in-kind support and maintenance updates that could impact their payment amounts. Previously, teleservice center representatives had to refer these reports to a field office for development at a later date and in some instances, the field office would have to recontact the claimant. This prior business process could result in delays in processing the report and potentially create an improper payment.
+We collect death data from a variety of sources and work to improve our death data processing so that we can effectively administer our programs. We have a contract with every State Bureau of Vital Statistics (the custodians for death records) and with some jurisdictions to provide us death data. Since 2002, we worked with States that want and are able to build a streamlined death registration process known as Electronic Death Registration (EDR). As of July 2025, all 50 States, New York City, Washington, D.C., Puerto Rico, and the Commonwealth of the Northern Mariana Islands report deaths through the EDR process. On September 30, 2024, we awarded a contract with the National Association for Public Health Statistics and Information Systems (NAPHSIS) on the acquisition of historical State death records. In FY 2025, we worked with NAPHSIS on establishing the infrastructure required to receive the historical death data. This multi-year effort will increase the accuracy, integrity, and completeness of our death data.
+In March and June 2025, we updated Numident records with additional death information for non-beneficiary individuals that were over 120 years of age when there was no death record present on the Numident. These efforts resulted in over 12 million death records being added to the Numident. In March 2025, we also provided the Internal Revenue Service a one-time file concerning individuals listed in the agency’s enumeration system who are age 120 or older based on available information as recorded in that system. Efforts are ongoing to update our Numident records for individuals over 100 years of age with death data. We also increased the frequency with which the agency provides updates concerning the full file of death information to the Bureau of the Fiscal Service for use in the Do Not Pay system.? We implemented this change (from weekly to daily) on April 1, 2025. In July 2025, we released a reminder to field office technicians to verify and record the death when a report of death on form DS-2060 U.S. Consular Report of Death Abroad is received.
+For root causes where the data or information needed to process a payment correctly does not exist or the agency is unable to access the data or information needed, we are establishing alternate sources of information. For example, we conducted 22 computer-matching agreements (CMA) with various Federal partners to help us determine eligibility and offset benefits for our programs. The total annual savings attributed to these CMAs is approximately $14.9 billion, with an annual cost of approximately $510 million, yielding a positive benefit-to-cost ratio of about $29 to $1. We plan to continue current CMAs that yield a positive cost-benefit ratio, expand effective CMAs to meet additional program needs, research current programs, work with internal stakeholders to identify data exchange needs, and pursue new data exchanges with potential partners. In December 2024 and April 2025, we held Data Exchange Community of Practice meetings. In FY 2026, we are working to reestablish the relationships with the current agency contacts, update the invitation list, and determine future topics for the meetings as resources allow.
+In the Office of the Inspector General’s report on agency compliance with the Payment Integrity Information Act in FY 2024, they included a recommendation that the agency complete the Foreign Travel Data (FTD) project. FTD is an agency application with direct access to the Department of Homeland Security’s (DHS) Arrival and Departure Information System with travel information that if the agency maximizes its use, will further uncover unreported U.S. absences that affect SSI eligibility; thus, increasing the detection of improper payments. Effective January 2026, we are expanding the use of FTD to citizens for redeterminations and during initial claims, before SSI payments are made in certain situations, and non-citizens during initial claims, before SSI payments are made, in all cases. We are engaging with DHS’s Customs and Border Protection (CBP) to discuss the viability of establishing an automated data exchange to receive FTD and finish the exchange project in early FY 2027.
+We have several broad-based initiatives in place or underway that are designed to ensure technician compliance with policy and improve payment accuracy.
+We complete SSI Transaction Accuracy Reviews (STAR) on a biennial basis to assist in assessing operational quality. STAR focuses the accuracy of non-medical adjudicative decisions in initial claims redeterminations, and limited issues and exclusively on field office compliance with documentation and developmental requirements found in the agency’s policies and procedures. STAR findings enhance our understanding of those improper payments that result directly from technician error and help identify potential recommendations for improvement. In December 2025, we will publish the review of FY 2024 case samples in the STAR report. We paused STAR in FY 2025 to concentrate on special studies projects. We have resumed STAR in FY 2026.
+In September 2024, we released the 21st Century PolicyNet (21CPN), which replaced PolicyNet, the 20+ year-old software platform that contains multiple applications and hosts tens of thousands of pages of policy instruction. The overall goals of 21CPN are an improved user experience, process efficiencies for the author, publisher, and researcher role, as well as improving searching capabilities, including the use of intelligent search. In December 2024, we launched improvements that introduced new message types, enhanced search functionalities, upgraded navigation features, included spell check for technician searches, and provided access to a variety of operational resources, archives, and margin notes. In April 2025, we successfully finished the data migration process and implemented enhanced search features. These improvements now encompass the hearings, appeal, and litigation law manual, as well as Social Security rulings and acquiescence rulings, along with policy documents and ownership details. Additionally, we provided quick access to agency form repositories and included a user guide for 21CPN. In June 2025, we launched an advanced search feature designed to improve the accessibility of policies, procedures, and instructions. Additionally, we upgraded the application's presentation and usability by incorporating a series of content clusters and a "Trending" topics section to showcase and highlight agency initiatives for key stakeholders. In September 2025, we broadened the data set to incorporate various procedural content clusters, link libraries, question and answer sections, and related instructions links. Furthermore, we improved the presentation functionality by introducing subscriptions and daily messages. Finally, by the end of FY 2026, contingent upon successful testing and evaluation, we plan to launch a generative AI "Policy Assistant Tool (PAT)" designed to simplify the search process for policies, procedures, and instructions. This tool will assist technicians in quickly and accurately finding and understanding relevant information to aid in decision-making.
+We continue development of the Consolidated Claims Experience (CCE), a modernized user-friendly web-based application designed to centralize and streamline benefit claim processing actions, reduce training time for technicians, and provide a more intuitive approach for data collection and processing of benefit claims. CCE will employ modernized and enhanced computation utilities that minimize manual tasks and help technicians identify entitlement and eligibility for all programs for which the claimant qualifies, in order to mitigate missed entitlements. The system introduces new and enhanced features not found in existing platforms, such as More Info links, talking points for users, and easy access to commonly used external resources. These improvements increase customer satisfaction by eliminating redundant information requests and reducing the need for technicians to recontact customers, improve the timeliness and accuracy of claims processing, enhancing efficiency, and reducing operating costs. In February 2025, the first phase of SSI payment continuation introduced a new automated Payment Continuation page to review and adjust protected payment levels when Goldberg/Kelly payment continuation applies and the requirement to build the Supplemental Security Record when a non-medical post-eligibility appeal is filed. In April 2025, users can now enter a date up to 10 years prior in the Protective and Effecting Filing date within the application screens. Prior to this release, there was a 6-year date system limitation. In FYs 2026-2027, work will continue on additional phases of the SSI payment continuation initiative to migrate functionality into the modern environment to lessen user errors, ensure correct/timely payments and reduce reliance on regionally developed appeals application.
+We developed the Technician Experience Dashboard (TED) as an enterprise customer relationship management solution that will provide a single location for information about our customers’ interactions with the agency to make it easier for our employees to help the public and increases efficiency and accuracy, improving the overall customer experience. In February 2024, we rolled TED out nationally to all field offices (FO) and workload support units. In November 2024, we expanded TED to all teleservice (TSC) centers. TED modernized the previous 30-year-old Customer Help and Information Program (CHIP) that assisted TSC technicians when responding to customer inquiries via telephone. In January and March 2025, we released two iterations of TED enhancements, improving upon the functionality for field office and teleservice centers. In April and June 2025, we enhanced the identity verifications procedures within TED to send a Security Authentication Personal Identification Number to authenticated customers (that technicians subsequently verify) before making direct deposit and direct express enrollments, changes, or cancellations over the phone.
+In December 2025, we plan to release a workflow in TED that allows FO and TSC technicians to update payment information for Supplemental Security Income (SSI) recipients. The release will also include the FO expansion of the ability to automate the process for collecting the customer SSN and starting an interaction in TED. In addition, TSC technicians will have the ability to access the workflow for handling customer requests for special notice options and other accommodations. Modernization efforts will also include the replacement of older technology used to pass data from legacy systems. In FY 2026, business workflow development efforts will focus on a streamlined process for assisting SSI recipients with updating address and telephone information, scheduling appointments and sending customers agency forms/links via their “my Social Security” account, text, or email. In addition, the product will continue to work towards CHIP replacement by implementing the use of artificial intelligence to develop high volume informational workflows such as Medicare, Social Security Statement etc. Lastly, we are working to implement the first iteration of Customer Intake in TED in FY 2026. This feature empowers technicians to seamlessly manage reception traffic and appointments for their office. With streamlined check-in, identity verification, and task management capabilities, technicians can deliver faster, more accurate and personalized service without switching between multiple applications.
+In March 2024, we expanded the Upload Documents and eSignature services, which allows beneficiaries and recipients to submit and sign documents electronically, to all field offices and workload support units nationwide. We completed various enhancements and expanded available forms throughout FYs 2024 and 2025. Beginning March 29, 2025, a new customer-initiated option is available allowing customers to electronically submit certain forms to the agency without technician initiation. This self-service approach empowers customers to initiate document uploads as soon as they recognize a need, eliminating delays caused by waiting for technician outreach. In FY 2026, we will continue to webify forms for a mobile friendly experience and increase the number of forms. We plan to expand customer-initiated submissions to allow individual representative payees to submit documents.
+In April 2025, we released a Video on Demand and Policy in Focus training and reminders for handling non-home real property resources such as the look-back period, documentation for property determinations and independent property verifications, undue hardship, and living arrangement changes from property conflicts. In May 2025, we published the permanent instructions on the SSI income policy treatment for types of assistance classified as pandemic-related disaster assistance and for types of assistance that are not. We also published the permanent policy instructions for developing and documenting SSI resource exclusions from pandemic-related disaster assistance.
+We are committed to ensuring recipients receive all payments due. Through the potential entitlement workload, we analyze data to determine groups of individuals where entitlement to a different record is possible, or entitlement to higher payments on the same record is possible. While potential entitlements are generally not underpayments but rather serve as a lead to explore additional entitlement, there is some intersection between these issues. In FY 2025, we took several actions to alert individuals of a potential entitlement to SSI. In October 2024, we released Dear Colleague Letter to advocates and published a blog, “SSA Talks: Benefits for Children (SSI and Survivors),” to announce an SSA Talks episode about the types of benefits and payments available to children. In January 2025, we released a blog sharing information that individuals may be able to receive SSI payments even if they already receive Social Security benefits. In FY 2026, we will continue to identify recipients with potential entitlement to higher payments and send notices to inform them. We will follow policies to develop for potential payments and explore entitlement for applicants on other records and other classes of payments where eligible.
+We provided resources for technicians to use when reviewing and processing requests for waiver of an overpayment. In February 2025, within an existing waiver processing toolkit, we added links to live waiver training sessions and an updated overpayment waiver decision tree. In June 2025, we created the updated SSA-632-BK, Request for Waiver of Overpayment Recovery, to streamline the process for submitting overpayment waiver requests and improve ease of use for the public. To improve timeliness and accuracy of processing overpayment and underpayment actions, in November 2024, we provided reminders to technicians on processing of manual SSI overpayment notices. In April 2025, we issued reminders regarding the review and release of SSI underpayments of $15,000 or more. As of September 30, 2025, we completed 98.12 percent of SSI underpayments that were identified as priority cases or pending for a year or more at the beginning of FY 2024. Including cases where installments have been initiated but are awaiting the release of remaining installment payments, our completion percentage increases to 99.36 percent.
+In FY 2024, we published the revised Notice Language Clearance Process policy, which incorporates review and approval of notice language through the plain language and the customer experience lens. In FY 2025, we used this new policy to provide a plain language review of 22 notices.
+The majority of Supplemental Security Income (SSI) Improper Payments occur when recipients (or their representative payees on their behalf) fail to timely or accurately report changes in any of their eligibility factors. improper payments can also occur because there is no database or dataset that currently exists where we can check eligibility factors prior to making the payment. For example, the law requires us to evaluate in-kind support and maintenance (ISM) that an individual receives, which is difficult to accurately value because in-kind assistance can fluctuate each month as household expenses, composition, and the type of assistance provided to a recipient may change. We rely on recipients to report changes in household expenses, composition, and contributions accurately and timely.
+For overpayments outside the agency’s control (approximately $5.7 billion), we are addressing the challenge of reliance on self-reporting by promoting timely wage reporting and issuing reminders on reporting responsibilities. We also began utilizing an automated information exchange with commercial payroll data providers to reduce the reliance on self-reporting of wages; this exchange is referred to as the Payroll Information Exchange.
+We monitor the status of improper payment corrective actions through recurring stakeholder and senior executive meetings. We evaluated existing initiatives and developed a comprehensive approach to identify, support, and prioritize new and planned reduction initiatives that target the root causes of leading causes of improper payments. The purpose of this effort is to strategically align agency wide initiatives that will have the most significant impact on the detection and prevention of improper payments. By identifying and analyzing the root causes of the improper payments, we channel our efforts in the most efficient manner ensuring that we are fiscally responsible as we implement a corrective action plan.
+We will continue to find opportunities to explore cost-effective corrective action plans based on our evaluations. However, we continue to note that the complexity of our SSI program makes it extremely difficult to determine the dollar value associated with a particular corrective action.</t>
+  </si>
+  <si>
+    <t>We developed the Improper Payment Alignment Strategy (IPAS) process to obtain agency-wide engagement and agreement on corrective actions to address the root causes of improper payments and the top deficiencies in our programs. We have completed IPASs on multiple areas of Old-Age and Survivors Insurance (OASI) improper payment deficiency, and we monitor the corrective actions within those IPASs. Most of the OASI corrective actions described within this response are from two new IPASs completed in FY 2025 (computations and relationship/dependency) as well as IPASs on windfall elimination provision (WEP) and government pension offset (GPO) and improving death data processes. We also discuss broad-based efforts to ensure policy compliance and payment accuracy and ensure individuals receive the benefits they are due.
+WEP and GPO reduced or offset Social Security monthly benefits to beneficiaries who received a pension based on non-covered earnings. Most of these workers had non-covered earnings from federal, state, or local governments. Errors relating to WEP/GPO have been one of the leading causes of OASI improper payments. We had previously relied on applicants, beneficiaries, or their representative payees to report their entitlement to current or future non-covered pensions; however, they did not always report the receipt of or changes to a pension, resulting in benefit calculation and payment errors. WEP and GPO errors also occurred when the agency did not correctly impose reductions or offset, misapplied exceptions or exemptions, or applied WEP but not GPO (or vice versa) for dually entitled beneficiaries.
+We developed a comprehensive corrective action plan to address multiple underlying causes of WEP/GPO improper payments. We assessed the root causes of improper payments based on these changes and developed policy, data, systems, and training solutions in line with each of the root causes of improper payments. On January 5, 2025, the Social Security Fairness Act of 2023 was signed into law, thereby repealing WEP/GPO. December 2023 is the last month that WEP and GPO will apply. This means that those rules no longer apply to benefits payable for January 2024 and later. The agency worked quickly and successfully to implement these changes. In April, we began releasing higher monthly benefit payments. As of July 7, 2025, we completed sending over 3.1 million payments, totaling $17 billion, to beneficiaries eligible under the Social Security Fairness Act. The average retroactive payment was $7,208. As of September 30, 2025, we have taken over 387,000 new initial claims. We anticipate the WEP/GPO repeal will significantly reduce and eventually eliminate WEP/GPO improper payments in future years.
+Computational errors occur due to many factors. Generally, these factors include: systems limitations for complex cases; manual calculation of benefits involving complicated policies; technician errors; incorrect earnings postings; beneficiaries not reporting complete and pertinent information; and lack of accurate and accessible data. We continue development of the Consolidated Claims Experience (CCE), a modernized user-friendly web-based application designed to centralize and streamline benefit claim processing actions, reduce training time for technicians, and provide a more intuitive approach for data collection and processing of benefit claims. CCE will employ modernized and enhanced computation utilities that minimize manual tasks and help technicians identify entitlement and eligibility for all programs for which the claimant qualifies, in order to mitigate missed entitlements. The system introduces new and enhanced features not found in existing platforms, such as More Info links, talking points for users, and easy access to commonly used external resources. These improvements increase customer satisfaction by eliminating redundant information requests and reducing the need for technicians to recontact customers, improve the timeliness and accuracy of claims processing, enhancing efficiency, and reducing operating costs. Between December 2024-August 2025, we released the retirement (RIB), Medicare-Only, and RIB with Medicare applications and user-requested enhancements in CCE to 14 sites in the Northeast and Mid-West/West regions.? We released these three applications nationally in CCE in September 2025.
+We developed processes using UIPath software to create automated “robotic” programs that perform routine or repetitive tasks and increase the speed and accuracy of manual processing. Robotic Processing Automation (RPA), or “BOTs,” are available to Processing Center (PC) technicians to assist with processing manual awards or post-entitlement actions. Since January 2021, seven PC-specific BOTs have been created to assist with OASI and/or Disability Insurance actions and placed into production. In December 2024, we provided general reminders and guidance for PC technicians on BOT usage. We completed the final testing stages of the UiPath Assistant software and rolled out the new platform to PC users in August 2025. We are making a long-term investment in robotics technology using the software to improve business processes and eliminate manual actions.
+In January 2025, we released instructions to field office technicians to review earning records for identified pending retirement and disability claims. Validating earnings records associated with pending claims ensures accurate eligibility and payment amounts. In April 2025, we released a reminder to frontline technicians including information on reducing improper payments related to benefit computations. When automated systems cannot compute benefit amounts in certain situations, there are a variety of computations tools that technicians should use to ensure accuracy. In May 2025, we updated policy instructions associated with temporary and ongoing earnings inaccuracies and coding used to trigger an alert for technicians to review and ensure the accuracy of earnings records and Primary Insurance Amounts before automatic benefit increases. In the May 2025 policy update, we expanded the coding to include “all disclaimed wages and those institutionalized.” This action stemmed from an Office of the Inspector General report on institutionalized beneficiaries who have earnings.
+Marital status and child relationship factors are material when determining entitlement to certain auxiliary and survivor benefits. Improper payments occur due to beneficiaries failing to report changes in marital status, the agency’s inability to automate, and difficulty expanding data exchanges to include the exchange of marital information. To address these issues, in FY 2025, we have been airing relationship and dependency reminders on televisions in field office reception areas. In April 2025, we released a reminder to frontline technicians on checking for program entitlement when an individual changes their name due to marriage or divorce. The guidance also included a reminder on verifying that all child-in-care information is entered in the system correctly. In FY 2026, if resources allow, we will explore options to expand the Internet Social Security Number Replacement’s current process and incorporate downstream application alerts to reduce instances of improper payments.
+We collect death data from a variety of sources and work to improve our death data processing so that we can effectively administer our programs. We have a contract with every State Bureau of Vital Statistics (the custodians for death records) and with some jurisdictions to provide us death data. Since 2002, we worked with States that want and are able to build a streamlined death registration process known as Electronic Death Registration (EDR). As of July 2025, all 50 States, New York City, Washington, D.C., Puerto Rico, and the Commonwealth of the Northern Mariana Islands report deaths through the EDR process. On September 30, 2024, we awarded a contract with the National Association for Public Health Statistics and Information Systems (NAPHSIS) on the acquisition of historical State death records. In FY 2025, we worked with NAPHSIS on establishing the infrastructure required to receive the historical death data. This multi-year effort will increase the accuracy, integrity, and completeness of our death data.
+In March and June 2025, we updated Numident records with additional death information for non-beneficiary individuals that were over 120 years of age when there was no death record present on the Numident. These efforts resulted in over 12 million death records being added to the Numident. In March 2025, we also provided the Internal Revenue Service a one-time file concerning individuals listed in the agency’s enumeration system who are age 120 or older based on available information as recorded in that system. Efforts are ongoing to update our Numident records for individuals over 100 years of age with death data. We also increased the frequency with which the agency provides updates concerning the full file of death information to the Bureau of the Fiscal Service for use in the Do Not Pay system.? We implemented this change (from weekly to daily) on April 1, 2025. In July 2025, we released a reminder to field office technicians to verify and record the death when a report of death on form DS-2060 U.S. Consular Report of Death Abroad is received.
+For root causes where the data or information needed to process a payment correctly does not exist or the agency is unable to access the data or information needed, we are establishing alternate sources of information. For example, we conducted 22 computer-matching agreements (CMA) with various Federal partners to help us determine eligibility and offset benefits for our programs. The total annual savings attributed to these CMAs is approximately $14.9 billion, with an annual cost of approximately $510 million, yielding a positive benefit-to-cost ratio of about $29 to $1. We plan to continue current CMAs that yield a positive cost-benefit ratio, expand effective CMAs to meet additional program needs, research current programs, work with internal stakeholders to identify data exchange needs, and pursue new data exchanges with potential partners. In December 2024 and April 2025, we held Data Exchange Community of Practice meetings. In FY 2026, we are working to reestablish the relationships with the current agency contacts, update the invitation list, and determine future topics for the meetings as resources allow.
+We have several broad-based initiatives in place or underway that are designed to ensure technician compliance with policy and improve payment accuracy.
+We complete Transaction Accuracy Reviews (TAR) on a triennial basis to assist in assessing operational quality. TAR focuses on a review of the nonmedical factors of entitlement and eligibility for OASI and DI payments in initial claims awards and disallowances. TAR findings provide insight to causes of improper payments and identify recommendations for improvement, which are shared with agency stakeholders. TAR is completed on a triennial basis. We will complete the next TAR report in FY 2027 based on reviews of FY 2026 case samples.
+In September 2024, we released the 21st Century PolicyNet (21CPN), which replaced PolicyNet, the 20+ year-old software platform that contains multiple applications and hosts tens of thousands of pages of policy instruction. The overall goals of 21CPN are an improved user experience, process efficiencies for the author, publisher, and researcher role, as well as improving searching capabilities, including the use of intelligent search. In December 2024, we launched improvements that introduced new message types, enhanced search functionalities, upgraded navigation features, included spell check for technician searches, and provided access to a variety of operational resources, archives, and margin notes. In April 2025, we successfully finished the data migration process and implemented enhanced search features. These improvements now encompass the hearings, appeal, and litigation law manual, as well as Social Security rulings and acquiescence rulings, along with policy documents and ownership details. Additionally, we provided quick access to agency form repositories and included a user guide for 21CPN. In June 2025, we launched an advanced search feature designed to improve the accessibility of policies, procedures, and instructions. Additionally, we upgraded the application's presentation and usability by incorporating a series of content clusters and a "Trending" topics section to showcase and highlight agency initiatives for key stakeholders. In September 2025, we broadened the data set to incorporate various procedural content clusters, link libraries, question and answer sections, and related instructions links. Furthermore, we improved the presentation functionality by introducing subscriptions and daily messages. Finally, by the end of FY 2026, contingent upon successful testing and evaluation, we plan to launch a generative artificial intelligence (AI) "Policy Assistant Tool (PAT)" designed to simplify the search process for policies, procedures, and instructions. This tool will assist technicians in quickly and accurately finding and understanding relevant information to aid in decision-making.
+We developed the Technician Experience Dashboard (TED) as an enterprise customer relationship management solution that will provide a single location for information about our customers’ interactions with the agency to make it easier for our employees to help the public and increases efficiency and accuracy, improving the overall customer experience. In February 2024, we rolled TED out nationally to all field offices (FO) and workload support units. In November 2024, we expanded TED to all teleservice (TSC) centers. TED modernized the previous 30-year-old Customer Help and Information Program (CHIP) that assisted TSC technicians when responding to customer inquiries via telephone. In January and March 2025, we released two iterations of TED enhancements, improving upon the functionality for field office and teleservice centers. In April and June 2025, we enhanced the identity verifications procedures within TED to send a Security Authentication Personal Identification Number to authenticated customers (that technicians subsequently verify) before making direct deposit and direct express enrollments, changes, or cancellations over the phone.
+In December 2025, we plan to release a workflow in TED that allows FO and TSC technicians to update payment information for Supplemental Security Income (SSI) recipients. The release will also include the FO expansion of the ability to automate the process for collecting the customer SSN and starting an interaction in TED. In addition, TSC technicians will have the ability to access the workflow for handling customer requests for special notice options and other accommodations. Modernization efforts will also include the replacement of older technology used to pass data from legacy systems. In FY 2026, business workflow development efforts will focus on a streamlined process for assisting SSI recipients with updating address and telephone information, scheduling appointments and sending customers agency forms/links via their “my Social Security” account, text, or email. In addition, the product will continue to work towards CHIP replacement by implementing the use of AI to develop high volume informational workflows such as Medicare, Social Security Statement etc. Lastly, we are working to implement the first iteration of Customer Intake in TED in FY 2026. This feature empowers technicians to seamlessly manage reception traffic and appointments for their office. With streamlined check-in, identity verification, and task management capabilities, technicians can deliver faster, more accurate and personalized service without switching between multiple applications.
+In March 2024, we expanded the Upload Documents and eSignature services, which allows beneficiaries and recipients to submit and sign documents electronically, to all field offices and workload support units nationwide. We completed various enhancements and expanded available forms throughout FYs 2024 and 2025. Beginning March 29, 2025, a new customer-initiated option is available allowing customers to electronically submit certain forms to the agency without technician initiation. This self-service approach empowers customers to initiate document uploads as soon as they recognize a need, eliminating delays caused by waiting for technician outreach. In FY 2026, we will continue to webify forms for a mobile friendly experience and increase the number of forms. We plan to expand customer-initiated submissions to allow individual representative payees to submit documents.
+To improve accuracy of processing overpayment actions, from July 2024 to September 2025, we conducted in-line quality reviews of almost 4,300 high-dollar overpayments exceeding $50,000. From September 2024 to September 2025, we conducted post adjudicative reviews of almost 9,400 overpayments exceeding $10,000. We make corrections to identified errors and use the analysis and findings to conduct training and issues reminders to processing center (PC) technicians. Additionally, in October 2024, we conducted a probe of recently processed overpayments to obtain a baseline accuracy, inform a further in-depth study, determine specific causes of overpayment errors, whether technicians and automated systems had difficulty processing one type of overpayment as compared to another, and to see the effects of changes made to the overpayment process based on prior quality reviews (e.g., requiring a second review for overpayments posted to a record in excess of $50,000). Based on the results of the probe, in May 2025, we began conducting a quality review of recently processed overpayments stratified by PC and providing case level feedback to the PCs. In spring 2026, we plan to provide overall accuracy findings to each PC, along with information on the errors identified, and recommendations for improvement. We are considering further reviews in FY 2026, dependent upon FY 2025 findings, available resources, and competing priorities.
+We provided resources for technicians to use when reviewing and processing requests for waiver of an overpayment. In February 2025, within an existing waiver processing toolkit, we added links to live waiver training sessions and an updated overpayment waiver decision tree. In June 2025, we created the updated SSA-632-BK, Request for Waiver of Overpayment Recovery, to streamline the process for submitting overpayment waiver requests and improve ease of use for the public.
+We are committed to ensuring beneficiaries receive all benefits due. Through the potential entitlement workload, we analyze data to determine groups of individuals where entitlement to a different record is possible, or entitlement to higher benefits on the same record is possible. While potential entitlements are generally not underpayments but rather serve as a lead to explore additional entitlement, there is some intersection between these issues. For example, we might identify a situation where a group of individuals is impacted by a systemic problem with our policy, processes or automation that results in underpayments on the current record (i.e.; benefit computation error), requiring further investigation and analysis, special outreach or handling.
+In October 2024, we released a Dear Colleague Letter to advocates and published a blog, “SSA Talks: Benefits for Children (SSI and Survivors),” to announce an SSA Talks episode about the types of benefits available to children. In October 2024 and April 2025, we sent notices to beneficiaries who are receiving spousal benefits but may have sufficient earnings to be eligible for higher retirement benefits based on their own earnings; and surviving spouses who are potentially eligible for higher retirement benefits on their own accounts. We released 20,000 mailers monthly from December 16, 2024, through February 2025 to households with minor children potentially eligible for a survivor benefit. In February 2025, we released annual mailers to beneficiaries whose benefits as a divorced spouse were terminated, but they now may be eligible to receive higher benefits as a surviving divorced spouse. In FY 2026, we will continue to identify beneficiaries with potential entitlement to higher benefits and send notices to inform them. We will follow policies to develop for potential benefits and explore entitlement for applicants on other records and other classes of benefits where eligible.
+In FY 2024, we published the revised Notice Language Clearance Process policy, which incorporates review and approval of notice language through the plain language and the customer experience lens. In FY 2025, we used this new policy to provide a plain language review of 22 notices.
+For the root cause of overpayments due to our failure to access data or information needed (approximately $1.1 billion), our corrective actions and strategies fall within several high-level categories such as automation, training, and cross enterprise sharing. For overpayments outside the agency’s control (approximately $67.2 million), we are addressing the challenge of reliance on self-reporting by promoting timely reporting of changes impacting benefit eligibility and payment amounts and issuing reminders on reporting responsibilities.
+We monitor the status of improper payment corrective actions through recurring stakeholder and senior executive meetings. We evaluated existing initiatives and developed a comprehensive approach to identify, support, and prioritize new and planned reduction initiatives that target the root causes of improper payments. The purpose of this effort is to strategically align agencywide initiatives that will have the most significant impact to the detection and prevention of improper payments. By identifying and analyzing the root causes of the improper payments, we channel our efforts in the most efficient manner ensuring that we are fiscally responsible as we implement a corrective action plan.
+We will continue to find opportunities to explore cost-effective corrective action plans based on our evaluations. However, we continue to note that the complexity of our Old-Age and Survivors Insurance program makes it extremely difficult to determine the dollar value associated with a particular corrective action.</t>
+  </si>
 </sst>
 </file>
 
@@ -3703,15 +3724,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3723,6 +3741,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12963,414 +12988,415 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.3984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="52.3984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.265625" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.265625" style="2" customWidth="1"/>
     <col min="4" max="4" width="35.3984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="6" width="35.3984375" style="11" customWidth="1"/>
-    <col min="7" max="9" width="9" style="12" customWidth="1"/>
-    <col min="10" max="10" width="12.1328125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="10.1328125" style="13" customWidth="1"/>
-    <col min="12" max="12" width="15.1328125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="35.3984375" style="10" customWidth="1"/>
+    <col min="7" max="9" width="9" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.1328125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="10.1328125" style="12" customWidth="1"/>
+    <col min="12" max="12" width="15.1328125" style="12" customWidth="1"/>
     <col min="13" max="16" width="9" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9" style="13" customWidth="1"/>
+    <col min="17" max="17" width="9" style="12" customWidth="1"/>
     <col min="18" max="18" width="9" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9" style="13" customWidth="1"/>
+    <col min="19" max="19" width="9" style="12" customWidth="1"/>
     <col min="20" max="20" width="12.46484375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="11.6640625" style="13" customWidth="1"/>
+    <col min="21" max="21" width="11.6640625" style="12" customWidth="1"/>
     <col min="22" max="22" width="9" style="2" customWidth="1"/>
-    <col min="23" max="23" width="9" style="13" customWidth="1"/>
+    <col min="23" max="23" width="9" style="12" customWidth="1"/>
     <col min="24" max="24" width="9" style="2" customWidth="1"/>
-    <col min="25" max="25" width="9" style="13" customWidth="1"/>
+    <col min="25" max="25" width="9" style="12" customWidth="1"/>
     <col min="26" max="26" width="9" style="2" customWidth="1"/>
-    <col min="27" max="27" width="9" style="13" customWidth="1"/>
+    <col min="27" max="27" width="9" style="12" customWidth="1"/>
     <col min="28" max="28" width="9" style="2" customWidth="1"/>
-    <col min="29" max="29" width="9" style="13" customWidth="1"/>
+    <col min="29" max="29" width="9" style="12" customWidth="1"/>
     <col min="30" max="30" width="9" style="2" customWidth="1"/>
-    <col min="31" max="31" width="9" style="13" customWidth="1"/>
+    <col min="31" max="31" width="9" style="12" customWidth="1"/>
     <col min="32" max="32" width="9" style="2" customWidth="1"/>
-    <col min="33" max="37" width="9" style="13" customWidth="1"/>
-    <col min="38" max="38" width="12.59765625" style="13" customWidth="1"/>
-    <col min="39" max="40" width="10.1328125" style="13" customWidth="1"/>
-    <col min="41" max="42" width="9.265625" style="13" customWidth="1"/>
+    <col min="33" max="37" width="9" style="12" customWidth="1"/>
+    <col min="38" max="38" width="12.59765625" style="12" customWidth="1"/>
+    <col min="39" max="40" width="10.1328125" style="12" customWidth="1"/>
+    <col min="41" max="42" width="9.265625" style="12" customWidth="1"/>
     <col min="43" max="43" width="9" style="2" customWidth="1"/>
-    <col min="44" max="44" width="9" style="13" customWidth="1"/>
+    <col min="44" max="44" width="9" style="12" customWidth="1"/>
     <col min="45" max="47" width="12.265625" style="2" customWidth="1"/>
-    <col min="48" max="52" width="9" style="2" customWidth="1"/>
+    <col min="48" max="48" width="25.53125" style="2" customWidth="1"/>
+    <col min="49" max="52" width="9" style="2" customWidth="1"/>
     <col min="53" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:52" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5" t="s">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15"/>
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15"/>
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15"/>
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15"/>
     </row>
     <row r="2" spans="1:52" ht="26.25" x14ac:dyDescent="0.45">
-      <c r="A2" s="6"/>
+      <c r="A2" s="5"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="T2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="V2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="W2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="X2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Y2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="Z2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AA2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AB2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AC2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AD2" s="7" t="s">
+      <c r="AD2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AE2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AF2" s="7" t="s">
+      <c r="AF2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AG2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AH2" s="7" t="s">
+      <c r="AH2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AI2" s="7" t="s">
+      <c r="AI2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AJ2" s="7" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AK2" s="7" t="s">
+      <c r="AK2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AL2" s="7" t="s">
+      <c r="AL2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM2" s="7" t="s">
+      <c r="AM2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AN2" s="7" t="s">
+      <c r="AN2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AO2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AP2" s="7" t="s">
+      <c r="AP2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AQ2" s="7" t="s">
+      <c r="AQ2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AR2" s="7" t="s">
+      <c r="AR2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AS2" s="7" t="s">
+      <c r="AS2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AT2" s="7" t="s">
+      <c r="AT2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AU2" s="7" t="s">
+      <c r="AU2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AV2" s="7" t="s">
+      <c r="AV2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AW2" s="7" t="s">
+      <c r="AW2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AX2" s="7" t="s">
+      <c r="AX2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AY2" s="7" t="s">
+      <c r="AY2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AZ2" s="7" t="s">
+      <c r="AZ2" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:52" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
-        <v>840</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="V3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="W3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="X3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Y3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="Z3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AA3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AB3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AC3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AD3" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AE3" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AF3" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AG3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AH3" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AI3" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="AJ3" s="7" t="s">
+      <c r="AJ3" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AK3" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AL3" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AM3" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AN3" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AO3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AP3" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="AQ3" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="AR3" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AS3" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="AT3" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="AU3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="AV3" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="AW3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="AX3" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="AY3" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="AZ3" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>102</v>
@@ -13418,10 +13444,10 @@
       <c r="S4" s="4">
         <v>23.9</v>
       </c>
-      <c r="T4" s="8">
+      <c r="T4" s="7">
         <v>45383</v>
       </c>
-      <c r="U4" s="8">
+      <c r="U4" s="7">
         <v>45747</v>
       </c>
       <c r="V4" s="4" t="s">
@@ -13508,7 +13534,7 @@
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>117</v>
@@ -13562,10 +13588,10 @@
       <c r="S5" s="4">
         <v>19.34</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T5" s="7">
         <v>45383</v>
       </c>
-      <c r="U5" s="8">
+      <c r="U5" s="7">
         <v>45747</v>
       </c>
       <c r="V5" s="4" t="s">
@@ -13656,7 +13682,7 @@
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>120</v>
@@ -13712,10 +13738,10 @@
       <c r="S6" s="4">
         <v>0</v>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="7">
         <v>44835</v>
       </c>
-      <c r="U6" s="8">
+      <c r="U6" s="7">
         <v>45199</v>
       </c>
       <c r="V6" s="4" t="s">
@@ -13802,7 +13828,7 @@
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>133</v>
@@ -13852,10 +13878,10 @@
       <c r="S7" s="4">
         <v>240.08131401</v>
       </c>
-      <c r="T7" s="8">
+      <c r="T7" s="7">
         <v>44835</v>
       </c>
-      <c r="U7" s="8">
+      <c r="U7" s="7">
         <v>45199</v>
       </c>
       <c r="V7" s="4" t="s">
@@ -13873,7 +13899,7 @@
       <c r="Z7" s="4">
         <v>20.396612990000001</v>
       </c>
-      <c r="AA7" s="9">
+      <c r="AA7" s="8">
         <v>9.5700181619069305E-2</v>
       </c>
       <c r="AB7" s="4">
@@ -13891,7 +13917,7 @@
       <c r="AF7" s="4">
         <v>20.396612990000001</v>
       </c>
-      <c r="AG7" s="9">
+      <c r="AG7" s="8">
         <v>9.5700181619069305E-2</v>
       </c>
       <c r="AH7" s="4">
@@ -13942,7 +13968,7 @@
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>143</v>
@@ -13992,13 +14018,13 @@
       <c r="S8" s="4">
         <v>0</v>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="7">
         <v>44835</v>
       </c>
-      <c r="U8" s="8">
+      <c r="U8" s="7">
         <v>45199</v>
       </c>
-      <c r="V8" s="10">
+      <c r="V8" s="9">
         <v>1</v>
       </c>
       <c r="W8" s="4">
@@ -14078,7 +14104,7 @@
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>154</v>
@@ -14134,10 +14160,10 @@
       <c r="S9" s="4">
         <v>646.85</v>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="7">
         <v>45474</v>
       </c>
-      <c r="U9" s="8">
+      <c r="U9" s="7">
         <v>45838</v>
       </c>
       <c r="V9" s="4" t="s">
@@ -14228,7 +14254,7 @@
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>169</v>
@@ -14282,10 +14308,10 @@
       <c r="S10" s="4">
         <v>0</v>
       </c>
-      <c r="T10" s="8">
+      <c r="T10" s="7">
         <v>45474</v>
       </c>
-      <c r="U10" s="8">
+      <c r="U10" s="7">
         <v>45838</v>
       </c>
       <c r="V10" s="4" t="s">
@@ -14372,7 +14398,7 @@
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>180</v>
@@ -14428,10 +14454,10 @@
       <c r="S11" s="4">
         <v>0</v>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="7">
         <v>45200</v>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="7">
         <v>45565</v>
       </c>
       <c r="V11" s="4" t="s">
@@ -14522,7 +14548,7 @@
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>192</v>
@@ -14572,10 +14598,10 @@
       <c r="S12" s="4">
         <v>0</v>
       </c>
-      <c r="T12" s="8">
+      <c r="T12" s="7">
         <v>45200</v>
       </c>
-      <c r="U12" s="8">
+      <c r="U12" s="7">
         <v>45565</v>
       </c>
       <c r="V12" s="4" t="s">
@@ -14658,7 +14684,7 @@
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>202</v>
@@ -14724,7 +14750,7 @@
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>206</v>
@@ -14772,10 +14798,10 @@
       <c r="S14" s="4">
         <v>28.91</v>
       </c>
-      <c r="T14" s="8">
+      <c r="T14" s="7">
         <v>45200</v>
       </c>
-      <c r="U14" s="8">
+      <c r="U14" s="7">
         <v>45565</v>
       </c>
       <c r="V14" s="4" t="s">
@@ -14793,7 +14819,7 @@
       <c r="Z14" s="4">
         <v>2.69</v>
       </c>
-      <c r="AA14" s="9">
+      <c r="AA14" s="8">
         <v>2.4173365264940901E-2</v>
       </c>
       <c r="AB14" s="4">
@@ -14866,7 +14892,7 @@
     </row>
     <row r="15" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>217</v>
@@ -14920,10 +14946,10 @@
       <c r="S15" s="4">
         <v>169.62</v>
       </c>
-      <c r="T15" s="8">
+      <c r="T15" s="7">
         <v>45200</v>
       </c>
-      <c r="U15" s="8">
+      <c r="U15" s="7">
         <v>45565</v>
       </c>
       <c r="V15" s="4" t="s">
@@ -14941,13 +14967,13 @@
       <c r="Z15" s="4">
         <v>3.52</v>
       </c>
-      <c r="AA15" s="9">
+      <c r="AA15" s="8">
         <v>1.56417422465727E-3</v>
       </c>
       <c r="AB15" s="4">
         <v>0.20538229684498499</v>
       </c>
-      <c r="AC15" s="9">
+      <c r="AC15" s="8">
         <v>7.5373645450672502E-2</v>
       </c>
       <c r="AD15" s="4">
@@ -15018,7 +15044,7 @@
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>225</v>
@@ -15084,7 +15110,7 @@
     </row>
     <row r="17" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>228</v>
@@ -15138,10 +15164,10 @@
       <c r="S17" s="4">
         <v>125.81</v>
       </c>
-      <c r="T17" s="8">
+      <c r="T17" s="7">
         <v>45474</v>
       </c>
-      <c r="U17" s="8">
+      <c r="U17" s="7">
         <v>45838</v>
       </c>
       <c r="V17" s="4" t="s">
@@ -15236,7 +15262,7 @@
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>236</v>
@@ -15290,10 +15316,10 @@
       <c r="S18" s="4">
         <v>28.29</v>
       </c>
-      <c r="T18" s="8">
+      <c r="T18" s="7">
         <v>45474</v>
       </c>
-      <c r="U18" s="8">
+      <c r="U18" s="7">
         <v>45838</v>
       </c>
       <c r="V18" s="4" t="s">
@@ -15388,7 +15414,7 @@
     </row>
     <row r="19" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>244</v>
@@ -15442,10 +15468,10 @@
       <c r="S19" s="4">
         <v>14.96</v>
       </c>
-      <c r="T19" s="8">
+      <c r="T19" s="7">
         <v>45474</v>
       </c>
-      <c r="U19" s="8">
+      <c r="U19" s="7">
         <v>45838</v>
       </c>
       <c r="V19" s="4" t="s">
@@ -15540,7 +15566,7 @@
     </row>
     <row r="20" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>253</v>
@@ -15594,10 +15620,10 @@
       <c r="S20" s="4">
         <v>0.82</v>
       </c>
-      <c r="T20" s="8">
+      <c r="T20" s="7">
         <v>45200</v>
       </c>
-      <c r="U20" s="8">
+      <c r="U20" s="7">
         <v>45565</v>
       </c>
       <c r="V20" s="4" t="s">
@@ -15692,7 +15718,7 @@
     </row>
     <row r="21" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>262</v>
@@ -15740,10 +15766,10 @@
       <c r="S21" s="4">
         <v>0</v>
       </c>
-      <c r="T21" s="8">
+      <c r="T21" s="7">
         <v>45200</v>
       </c>
-      <c r="U21" s="8">
+      <c r="U21" s="7">
         <v>45565</v>
       </c>
       <c r="V21" s="4" t="s">
@@ -15761,7 +15787,7 @@
       <c r="Z21" s="4">
         <v>2.36</v>
       </c>
-      <c r="AA21" s="9">
+      <c r="AA21" s="8">
         <v>4.2468751726417696E-3</v>
       </c>
       <c r="AB21" s="4">
@@ -15779,10 +15805,10 @@
       <c r="AF21" s="4">
         <v>2.36</v>
       </c>
-      <c r="AG21" s="9">
+      <c r="AG21" s="8">
         <v>4.2468751726417696E-3</v>
       </c>
-      <c r="AH21" s="9">
+      <c r="AH21" s="8">
         <v>4.2468751726417696E-3</v>
       </c>
       <c r="AI21" s="4">
@@ -15826,7 +15852,7 @@
     </row>
     <row r="22" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>272</v>
@@ -15882,10 +15908,10 @@
       <c r="S22" s="4">
         <v>5.91</v>
       </c>
-      <c r="T22" s="8">
+      <c r="T22" s="7">
         <v>45200</v>
       </c>
-      <c r="U22" s="8">
+      <c r="U22" s="7">
         <v>45565</v>
       </c>
       <c r="V22" s="4" t="s">
@@ -15906,10 +15932,10 @@
       <c r="AA22" s="4">
         <v>0.84556172122280504</v>
       </c>
-      <c r="AB22" s="9">
+      <c r="AB22" s="8">
         <v>1.53501742858287E-2</v>
       </c>
-      <c r="AC22" s="9">
+      <c r="AC22" s="8">
         <v>1.47992708041187E-2</v>
       </c>
       <c r="AD22" s="4">
@@ -15980,7 +16006,7 @@
     </row>
     <row r="23" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>284</v>
@@ -16036,10 +16062,10 @@
       <c r="S23" s="4">
         <v>3.4</v>
       </c>
-      <c r="T23" s="8">
+      <c r="T23" s="7">
         <v>45200</v>
       </c>
-      <c r="U23" s="8">
+      <c r="U23" s="7">
         <v>45565</v>
       </c>
       <c r="V23" s="4" t="s">
@@ -16060,10 +16086,10 @@
       <c r="AA23" s="4">
         <v>0.230890478736058</v>
       </c>
-      <c r="AB23" s="9">
+      <c r="AB23" s="8">
         <v>1.2760116244548101E-2</v>
       </c>
-      <c r="AC23" s="9">
+      <c r="AC23" s="8">
         <v>3.7692784736284598E-3</v>
       </c>
       <c r="AD23" s="4">
@@ -16134,7 +16160,7 @@
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>290</v>
@@ -16188,10 +16214,10 @@
       <c r="S24" s="4">
         <v>0</v>
       </c>
-      <c r="T24" s="8">
+      <c r="T24" s="7">
         <v>44927</v>
       </c>
-      <c r="U24" s="8">
+      <c r="U24" s="7">
         <v>45291</v>
       </c>
       <c r="V24" s="4" t="s">
@@ -16278,7 +16304,7 @@
     </row>
     <row r="25" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>301</v>
@@ -16326,10 +16352,10 @@
       <c r="S25" s="4">
         <v>0</v>
       </c>
-      <c r="T25" s="8">
+      <c r="T25" s="7">
         <v>45292</v>
       </c>
-      <c r="U25" s="8">
+      <c r="U25" s="7">
         <v>45657</v>
       </c>
       <c r="V25" s="4" t="s">
@@ -16412,7 +16438,7 @@
     </row>
     <row r="26" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>310</v>
@@ -16468,10 +16494,10 @@
       <c r="S26" s="4">
         <v>0</v>
       </c>
-      <c r="T26" s="8">
+      <c r="T26" s="7">
         <v>45200</v>
       </c>
-      <c r="U26" s="8">
+      <c r="U26" s="7">
         <v>45565</v>
       </c>
       <c r="V26" s="4" t="s">
@@ -16558,7 +16584,7 @@
     </row>
     <row r="27" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>321</v>
@@ -16614,10 +16640,10 @@
       <c r="S27" s="4">
         <v>0</v>
       </c>
-      <c r="T27" s="8">
+      <c r="T27" s="7">
         <v>45444</v>
       </c>
-      <c r="U27" s="8">
+      <c r="U27" s="7">
         <v>45808</v>
       </c>
       <c r="V27" s="4" t="s">
@@ -16706,7 +16732,7 @@
     </row>
     <row r="28" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>333</v>
@@ -16762,10 +16788,10 @@
       <c r="S28" s="4">
         <v>1010.33</v>
       </c>
-      <c r="T28" s="8">
+      <c r="T28" s="7">
         <v>45200</v>
       </c>
-      <c r="U28" s="8">
+      <c r="U28" s="7">
         <v>45565</v>
       </c>
       <c r="V28" s="4" t="s">
@@ -16783,10 +16809,10 @@
       <c r="Z28" s="4">
         <v>2.69</v>
       </c>
-      <c r="AA28" s="9">
+      <c r="AA28" s="8">
         <v>2.2939104777985199E-2</v>
       </c>
-      <c r="AB28" s="9">
+      <c r="AB28" s="8">
         <v>4.6645688897984899E-2</v>
       </c>
       <c r="AC28" s="4">
@@ -16860,7 +16886,7 @@
     </row>
     <row r="29" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>344</v>
@@ -16928,7 +16954,7 @@
     </row>
     <row r="30" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>348</v>
@@ -16978,10 +17004,10 @@
       <c r="S30" s="4">
         <v>0</v>
       </c>
-      <c r="T30" s="8">
+      <c r="T30" s="7">
         <v>44927</v>
       </c>
-      <c r="U30" s="8">
+      <c r="U30" s="7">
         <v>45291</v>
       </c>
       <c r="V30" s="4" t="s">
@@ -17068,7 +17094,7 @@
     </row>
     <row r="31" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>359</v>
@@ -17122,10 +17148,10 @@
       <c r="S31" s="4">
         <v>0</v>
       </c>
-      <c r="T31" s="8">
+      <c r="T31" s="7">
         <v>45108</v>
       </c>
-      <c r="U31" s="8">
+      <c r="U31" s="7">
         <v>45473</v>
       </c>
       <c r="V31" s="4" t="s">
@@ -17146,7 +17172,7 @@
       <c r="AA31" s="4">
         <v>6.7087968</v>
       </c>
-      <c r="AB31" s="9">
+      <c r="AB31" s="8">
         <v>2.9453799999999999E-2</v>
       </c>
       <c r="AC31" s="4">
@@ -17216,7 +17242,7 @@
     </row>
     <row r="32" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>369</v>
@@ -17270,10 +17296,10 @@
       <c r="S32" s="4">
         <v>0</v>
       </c>
-      <c r="T32" s="8">
+      <c r="T32" s="7">
         <v>45108</v>
       </c>
-      <c r="U32" s="8">
+      <c r="U32" s="7">
         <v>45473</v>
       </c>
       <c r="V32" s="4" t="s">
@@ -17294,7 +17320,7 @@
       <c r="AA32" s="4">
         <v>5.7332613493796396</v>
       </c>
-      <c r="AB32" s="9">
+      <c r="AB32" s="8">
         <v>4.2022100531529202E-2</v>
       </c>
       <c r="AC32" s="4">
@@ -17364,7 +17390,7 @@
     </row>
     <row r="33" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>377</v>
@@ -17420,10 +17446,10 @@
       <c r="S33" s="4">
         <v>0</v>
       </c>
-      <c r="T33" s="8">
+      <c r="T33" s="7">
         <v>44927</v>
       </c>
-      <c r="U33" s="8">
+      <c r="U33" s="7">
         <v>45291</v>
       </c>
       <c r="V33" s="4" t="s">
@@ -17510,7 +17536,7 @@
     </row>
     <row r="34" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>387</v>
@@ -17566,10 +17592,10 @@
       <c r="S34" s="4">
         <v>0</v>
       </c>
-      <c r="T34" s="8">
+      <c r="T34" s="7">
         <v>45108</v>
       </c>
-      <c r="U34" s="8">
+      <c r="U34" s="7">
         <v>45473</v>
       </c>
       <c r="V34" s="4" t="s">
@@ -17656,7 +17682,7 @@
     </row>
     <row r="35" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A35" s="4" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>397</v>
@@ -17712,10 +17738,10 @@
       <c r="S35" s="4">
         <v>0</v>
       </c>
-      <c r="T35" s="8">
+      <c r="T35" s="7">
         <v>44927</v>
       </c>
-      <c r="U35" s="8">
+      <c r="U35" s="7">
         <v>45291</v>
       </c>
       <c r="V35" s="4" t="s">
@@ -17800,156 +17826,156 @@
         <v>405</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.45">
-      <c r="A36" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="B36" s="4" t="s">
+    <row r="36" spans="1:52" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="14" t="s">
+        <v>795</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="14">
         <v>2025</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4" t="s">
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="14">
         <v>16458.25</v>
       </c>
-      <c r="O36" s="4">
-        <v>0</v>
-      </c>
-      <c r="P36" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="4">
-        <v>0</v>
-      </c>
-      <c r="R36" s="4">
-        <v>0</v>
-      </c>
-      <c r="S36" s="4">
+      <c r="O36" s="14">
+        <v>0</v>
+      </c>
+      <c r="P36" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="14">
+        <v>0</v>
+      </c>
+      <c r="R36" s="14">
+        <v>0</v>
+      </c>
+      <c r="S36" s="14">
         <v>4346.8100000000004</v>
       </c>
-      <c r="T36" s="8">
+      <c r="T36" s="16">
         <v>45200</v>
       </c>
-      <c r="U36" s="8">
+      <c r="U36" s="16">
         <v>45565</v>
       </c>
-      <c r="V36" s="4" t="s">
+      <c r="V36" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="W36" s="4">
-        <v>0</v>
-      </c>
-      <c r="X36" s="4" t="s">
+      <c r="W36" s="14">
+        <v>0</v>
+      </c>
+      <c r="X36" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="Y36" s="4">
+      <c r="Y36" s="14">
         <v>10</v>
       </c>
-      <c r="Z36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="4">
+      <c r="Z36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="14">
         <v>26.411131195600898</v>
       </c>
-      <c r="AD36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="4">
+      <c r="AD36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="14">
         <v>26.411131195600898</v>
       </c>
-      <c r="AI36" s="4">
+      <c r="AI36" s="14">
         <v>4346.8100000000004</v>
       </c>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="4" t="s">
+      <c r="AJ36" s="14"/>
+      <c r="AK36" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="AL36" s="4" t="s">
+      <c r="AL36" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="4"/>
-      <c r="AP36" s="4"/>
-      <c r="AQ36" s="4" t="s">
+      <c r="AM36" s="14"/>
+      <c r="AN36" s="14"/>
+      <c r="AO36" s="14"/>
+      <c r="AP36" s="14"/>
+      <c r="AQ36" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="AR36" s="4" t="s">
+      <c r="AR36" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="AS36" s="4"/>
-      <c r="AT36" s="4"/>
-      <c r="AU36" s="4" t="s">
+      <c r="AS36" s="14"/>
+      <c r="AT36" s="14"/>
+      <c r="AU36" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="AV36" s="4" t="s">
+      <c r="AV36" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="AW36" s="4" t="s">
+      <c r="AW36" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="AX36" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="AX36" s="4" t="s">
+      <c r="AY36" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="AY36" s="4" t="s">
+      <c r="AZ36" s="14" t="s">
         <v>419</v>
-      </c>
-      <c r="AZ36" s="4" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="37" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>407</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E37" s="4">
         <v>2025</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -17958,7 +17984,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N37" s="4">
         <v>33980.76</v>
@@ -17978,10 +18004,10 @@
       <c r="S37" s="4">
         <v>1481.23</v>
       </c>
-      <c r="T37" s="8">
+      <c r="T37" s="7">
         <v>45200</v>
       </c>
-      <c r="U37" s="8">
+      <c r="U37" s="7">
         <v>45565</v>
       </c>
       <c r="V37" s="4" t="s">
@@ -18028,10 +18054,10 @@
       </c>
       <c r="AJ37" s="4"/>
       <c r="AK37" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AL37" s="4" t="s">
-        <v>426</v>
+        <v>837</v>
       </c>
       <c r="AM37" s="4"/>
       <c r="AN37" s="4"/>
@@ -18041,193 +18067,193 @@
         <v>393</v>
       </c>
       <c r="AR37" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AS37" s="4"/>
       <c r="AT37" s="4"/>
-      <c r="AU37" s="4" t="s">
+      <c r="AU37" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="AV37" s="4" t="s">
+      <c r="AV37" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="AW37" s="4" t="s">
+      <c r="AW37" s="14" t="s">
+        <v>836</v>
+      </c>
+      <c r="AX37" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="AY37" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="AZ37" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="38" spans="1:52" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="14" t="s">
+        <v>797</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="AX37" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="AY37" s="4" t="s">
+      <c r="C38" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="AZ37" s="4" t="s">
+      <c r="D38" s="14" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.45">
-      <c r="A38" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="B38" s="4" t="s">
+      <c r="E38" s="14">
+        <v>2025</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="H38" s="14">
+        <v>7.5819999999999999</v>
+      </c>
+      <c r="I38" s="14">
+        <v>18.361000000000001</v>
+      </c>
+      <c r="J38" s="14">
+        <v>0</v>
+      </c>
+      <c r="K38" s="14">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="L38" s="14">
+        <v>26.77</v>
+      </c>
+      <c r="M38" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="N38" s="14">
+        <v>67219.3</v>
+      </c>
+      <c r="O38" s="14">
+        <v>0</v>
+      </c>
+      <c r="P38" s="14">
+        <v>26.908999999999999</v>
+      </c>
+      <c r="Q38" s="14">
+        <v>26.297000000000001</v>
+      </c>
+      <c r="R38" s="14">
+        <v>18.184999999999999</v>
+      </c>
+      <c r="S38" s="14">
+        <v>23.44</v>
+      </c>
+      <c r="T38" s="16">
+        <v>45200</v>
+      </c>
+      <c r="U38" s="16">
+        <v>45657</v>
+      </c>
+      <c r="V38" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="W38" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="X38" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y38" s="14">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Z38" s="14">
+        <v>26.908999999999999</v>
+      </c>
+      <c r="AA38" s="18">
+        <v>4.0031657574535799E-2</v>
+      </c>
+      <c r="AB38" s="18">
+        <v>3.91212047730339E-2</v>
+      </c>
+      <c r="AC38" s="18">
+        <v>3.4870937364715103E-2</v>
+      </c>
+      <c r="AD38" s="18">
+        <v>2.7053242149204099E-2</v>
+      </c>
+      <c r="AE38" s="14">
+        <v>44.481999999999999</v>
+      </c>
+      <c r="AF38" s="14">
+        <v>71.391000000000005</v>
+      </c>
+      <c r="AG38" s="14">
+        <v>0.10620610449677401</v>
+      </c>
+      <c r="AH38" s="14">
+        <v>0.14107704186148901</v>
+      </c>
+      <c r="AI38" s="14">
+        <v>94.831000000000003</v>
+      </c>
+      <c r="AJ38" s="14"/>
+      <c r="AK38" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="AL38" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="E38" s="4">
-        <v>2025</v>
-      </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4">
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="H38" s="4">
-        <v>7.5819999999999999</v>
-      </c>
-      <c r="I38" s="4">
-        <v>18.361000000000001</v>
-      </c>
-      <c r="J38" s="4">
-        <v>0</v>
-      </c>
-      <c r="K38" s="4">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="L38" s="4">
-        <v>26.77</v>
-      </c>
-      <c r="M38" s="4" t="s">
+      <c r="AM38" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="AN38" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="AO38" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="N38" s="4">
-        <v>67219.3</v>
-      </c>
-      <c r="O38" s="4">
-        <v>0</v>
-      </c>
-      <c r="P38" s="4">
-        <v>26.908999999999999</v>
-      </c>
-      <c r="Q38" s="4">
-        <v>26.297000000000001</v>
-      </c>
-      <c r="R38" s="4">
-        <v>18.184999999999999</v>
-      </c>
-      <c r="S38" s="4">
-        <v>23.44</v>
-      </c>
-      <c r="T38" s="8">
-        <v>45575</v>
-      </c>
-      <c r="U38" s="8">
-        <v>45657</v>
-      </c>
-      <c r="V38" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="W38" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="X38" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y38" s="4">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Z38" s="4">
-        <v>26.908999999999999</v>
-      </c>
-      <c r="AA38" s="9">
-        <v>4.0031657574535799E-2</v>
-      </c>
-      <c r="AB38" s="9">
-        <v>3.91212047730339E-2</v>
-      </c>
-      <c r="AC38" s="9">
-        <v>3.4870937364715103E-2</v>
-      </c>
-      <c r="AD38" s="9">
-        <v>2.7053242149204099E-2</v>
-      </c>
-      <c r="AE38" s="4">
-        <v>44.481999999999999</v>
-      </c>
-      <c r="AF38" s="4">
-        <v>71.391000000000005</v>
-      </c>
-      <c r="AG38" s="4">
-        <v>0.10620610449677401</v>
-      </c>
-      <c r="AH38" s="4">
-        <v>0.14107704186148901</v>
-      </c>
-      <c r="AI38" s="4">
-        <v>94.831000000000003</v>
-      </c>
-      <c r="AJ38" s="4"/>
-      <c r="AK38" s="4" t="s">
+      <c r="AP38" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ38" s="14" t="s">
         <v>435</v>
       </c>
-      <c r="AL38" s="4" t="s">
+      <c r="AR38" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="AS38" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="AT38" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="AU38" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="AV38" s="14"/>
+      <c r="AW38" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="AM38" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="AN38" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="AO38" s="4" t="s">
+      <c r="AX38" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="AP38" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ38" s="4" t="s">
+      <c r="AY38" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="AR38" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="AS38" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="AT38" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AU38" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="AV38" s="4"/>
-      <c r="AW38" s="4" t="s">
+      <c r="AZ38" s="14" t="s">
         <v>439</v>
-      </c>
-      <c r="AX38" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="AY38" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="AZ38" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="39" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A39" s="4" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E39" s="4">
         <v>2025</v>
@@ -18252,7 +18278,7 @@
         <v>265.22000000000003</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N39" s="4">
         <v>109364.53</v>
@@ -18272,10 +18298,10 @@
       <c r="S39" s="4">
         <v>13.99</v>
       </c>
-      <c r="T39" s="8">
+      <c r="T39" s="7">
         <v>45566</v>
       </c>
-      <c r="U39" s="8">
+      <c r="U39" s="7">
         <v>45930</v>
       </c>
       <c r="V39" s="4" t="s">
@@ -18296,10 +18322,10 @@
       <c r="AA39" s="4">
         <v>0.24251007159268101</v>
       </c>
-      <c r="AB39" s="9">
+      <c r="AB39" s="8">
         <v>9.0303501510041601E-2</v>
       </c>
-      <c r="AC39" s="9">
+      <c r="AC39" s="8">
         <v>1.2792081674012501E-2</v>
       </c>
       <c r="AD39" s="4">
@@ -18322,10 +18348,10 @@
       </c>
       <c r="AJ39" s="4"/>
       <c r="AK39" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AL39" s="4" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AM39" s="4" t="s">
         <v>149</v>
@@ -18348,34 +18374,34 @@
         <v>149</v>
       </c>
       <c r="AU39" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AV39" s="4"/>
       <c r="AW39" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="AX39" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="AY39" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="AZ39" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="AX39" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="AY39" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="AZ39" s="4" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="40" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A40" s="4" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E40" s="4">
         <v>2025</v>
@@ -18388,7 +18414,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N40" s="4">
         <v>26614.887999999999</v>
@@ -18408,10 +18434,10 @@
       <c r="S40" s="4">
         <v>0</v>
       </c>
-      <c r="T40" s="8">
+      <c r="T40" s="7">
         <v>45383</v>
       </c>
-      <c r="U40" s="8">
+      <c r="U40" s="7">
         <v>45747</v>
       </c>
       <c r="V40" s="4" t="s">
@@ -18458,10 +18484,10 @@
       </c>
       <c r="AJ40" s="4"/>
       <c r="AK40" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AL40" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AM40" s="4"/>
       <c r="AN40" s="4"/>
@@ -18476,36 +18502,36 @@
       <c r="AS40" s="4"/>
       <c r="AT40" s="4"/>
       <c r="AU40" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="AV40" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="AW40" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX40" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="AV40" s="4" t="s">
+      <c r="AY40" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="AW40" s="4" t="s">
+      <c r="AZ40" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="AX40" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="AY40" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="AZ40" s="4" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A41" s="4" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E41" s="4">
         <v>2025</v>
@@ -18530,7 +18556,7 @@
         <v>17.132999999999999</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="N41" s="4">
         <v>2115.5</v>
@@ -18550,10 +18576,10 @@
       <c r="S41" s="4">
         <v>9.3119999999999994</v>
       </c>
-      <c r="T41" s="8">
+      <c r="T41" s="7">
         <v>45383</v>
       </c>
-      <c r="U41" s="8">
+      <c r="U41" s="7">
         <v>45747</v>
       </c>
       <c r="V41" s="4" t="s">
@@ -18600,10 +18626,10 @@
       </c>
       <c r="AJ41" s="4"/>
       <c r="AK41" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AL41" s="4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AM41" s="4" t="s">
         <v>233</v>
@@ -18626,36 +18652,36 @@
         <v>233</v>
       </c>
       <c r="AU41" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AV41" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="AW41" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="AX41" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="AY41" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="AW41" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="AX41" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="AY41" s="4" t="s">
-        <v>473</v>
-      </c>
       <c r="AZ41" s="4" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="42" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A42" s="4" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E42" s="4">
         <v>2025</v>
@@ -18668,7 +18694,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N42" s="4">
         <v>7392.0410000000002</v>
@@ -18688,10 +18714,10 @@
       <c r="S42" s="4">
         <v>0</v>
       </c>
-      <c r="T42" s="8">
+      <c r="T42" s="7">
         <v>45383</v>
       </c>
-      <c r="U42" s="8">
+      <c r="U42" s="7">
         <v>45747</v>
       </c>
       <c r="V42" s="4" t="s">
@@ -18738,10 +18764,10 @@
       </c>
       <c r="AJ42" s="4"/>
       <c r="AK42" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AL42" s="4" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AM42" s="4"/>
       <c r="AN42" s="4"/>
@@ -18756,34 +18782,34 @@
       <c r="AS42" s="4"/>
       <c r="AT42" s="4"/>
       <c r="AU42" s="4" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AV42" s="4"/>
       <c r="AW42" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AX42" s="4" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AY42" s="4" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AZ42" s="4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A43" s="4" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E43" s="4">
         <v>2025</v>
@@ -18808,7 +18834,7 @@
         <v>125.077</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N43" s="4">
         <v>3223.8159999999998</v>
@@ -18828,10 +18854,10 @@
       <c r="S43" s="4">
         <v>0</v>
       </c>
-      <c r="T43" s="8">
+      <c r="T43" s="7">
         <v>45383</v>
       </c>
-      <c r="U43" s="8">
+      <c r="U43" s="7">
         <v>45747</v>
       </c>
       <c r="V43" s="4" t="s">
@@ -18878,10 +18904,10 @@
       </c>
       <c r="AJ43" s="4"/>
       <c r="AK43" s="4" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AL43" s="4" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AM43" s="4" t="s">
         <v>110</v>
@@ -18904,30 +18930,30 @@
       </c>
       <c r="AV43" s="4"/>
       <c r="AW43" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AX43" s="4" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AY43" s="4" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AZ43" s="4" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A44" s="4" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E44" s="4">
         <v>2025</v>
@@ -18952,7 +18978,7 @@
         <v>57.064</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N44" s="4">
         <v>303.85199999999998</v>
@@ -18972,10 +18998,10 @@
       <c r="S44" s="4">
         <v>0.52800000000000002</v>
       </c>
-      <c r="T44" s="8">
+      <c r="T44" s="7">
         <v>45383</v>
       </c>
-      <c r="U44" s="8">
+      <c r="U44" s="7">
         <v>45747</v>
       </c>
       <c r="V44" s="4" t="s">
@@ -19022,10 +19048,10 @@
       </c>
       <c r="AJ44" s="4"/>
       <c r="AK44" s="4" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AL44" s="4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AM44" s="4" t="s">
         <v>149</v>
@@ -19052,30 +19078,30 @@
       </c>
       <c r="AV44" s="4"/>
       <c r="AW44" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="AX44" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="AY44" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="AZ44" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="AX44" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="AY44" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="AZ44" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="45" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A45" s="4" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E45" s="4">
         <v>2025</v>
@@ -19094,7 +19120,7 @@
         <v>65.462000000000003</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="N45" s="4">
         <v>1398.23</v>
@@ -19114,10 +19140,10 @@
       <c r="S45" s="4">
         <v>113.443</v>
       </c>
-      <c r="T45" s="8">
+      <c r="T45" s="7">
         <v>45383</v>
       </c>
-      <c r="U45" s="8">
+      <c r="U45" s="7">
         <v>45747</v>
       </c>
       <c r="V45" s="4" t="s">
@@ -19164,10 +19190,10 @@
       </c>
       <c r="AJ45" s="4"/>
       <c r="AK45" s="4" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AL45" s="4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AM45" s="4"/>
       <c r="AN45" s="4"/>
@@ -19190,36 +19216,36 @@
       </c>
       <c r="AV45" s="4"/>
       <c r="AW45" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="AX45" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="AY45" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="AZ45" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="AX45" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="AY45" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="AZ45" s="4" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="46" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E46" s="4">
         <v>2025</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -19234,7 +19260,7 @@
         <v>36.478999999999999</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="N46" s="4">
         <v>10585.147000000001</v>
@@ -19254,10 +19280,10 @@
       <c r="S46" s="4">
         <v>0</v>
       </c>
-      <c r="T46" s="8">
+      <c r="T46" s="7">
         <v>43922</v>
       </c>
-      <c r="U46" s="8">
+      <c r="U46" s="7">
         <v>45747</v>
       </c>
       <c r="V46" s="4" t="s">
@@ -19304,10 +19330,10 @@
       </c>
       <c r="AJ46" s="4"/>
       <c r="AK46" s="4" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AL46" s="4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AM46" s="4"/>
       <c r="AN46" s="4"/>
@@ -19326,36 +19352,36 @@
       </c>
       <c r="AV46" s="4"/>
       <c r="AW46" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="AX46" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="AY46" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ46" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="AX46" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="AY46" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="AZ46" s="4" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E47" s="4">
         <v>2025</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="G47" s="4">
         <v>0</v>
@@ -19376,7 +19402,7 @@
         <v>4484.6369999999997</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N47" s="4">
         <v>14604.947</v>
@@ -19396,10 +19422,10 @@
       <c r="S47" s="4">
         <v>4242.6859999999997</v>
       </c>
-      <c r="T47" s="8">
+      <c r="T47" s="7">
         <v>44287</v>
       </c>
-      <c r="U47" s="8">
+      <c r="U47" s="7">
         <v>45382</v>
       </c>
       <c r="V47" s="4" t="s">
@@ -19446,10 +19472,10 @@
       </c>
       <c r="AJ47" s="4"/>
       <c r="AK47" s="4" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AL47" s="4" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AM47" s="4" t="s">
         <v>111</v>
@@ -19473,43 +19499,43 @@
         <v>111</v>
       </c>
       <c r="AT47" s="4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AU47" s="4" t="s">
         <v>112</v>
       </c>
       <c r="AV47" s="4"/>
       <c r="AW47" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="AX47" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="AY47" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="AZ47" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="AX47" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="AY47" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="AZ47" s="4" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="48" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E48" s="4">
         <v>2025</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G48" s="4">
         <v>0</v>
@@ -19530,7 +19556,7 @@
         <v>927.24802112999998</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="N48" s="4">
         <v>143442.52010848001</v>
@@ -19550,10 +19576,10 @@
       <c r="S48" s="4">
         <v>0</v>
       </c>
-      <c r="T48" s="8">
+      <c r="T48" s="7">
         <v>45200</v>
       </c>
-      <c r="U48" s="8">
+      <c r="U48" s="7">
         <v>45565</v>
       </c>
       <c r="V48" s="4" t="s">
@@ -19600,62 +19626,62 @@
       </c>
       <c r="AJ48" s="4"/>
       <c r="AK48" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="AL48" s="4" t="s">
-        <v>536</v>
+        <v>532</v>
+      </c>
+      <c r="AL48" s="14" t="s">
+        <v>838</v>
       </c>
       <c r="AM48" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AN48" s="4" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AO48" s="4"/>
       <c r="AP48" s="4"/>
       <c r="AQ48" s="4"/>
       <c r="AR48" s="4"/>
       <c r="AS48" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AT48" s="4" t="s">
         <v>162</v>
       </c>
       <c r="AU48" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AV48" s="4"/>
       <c r="AW48" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AX48" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AY48" s="4" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AZ48" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="49" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E49" s="4">
         <v>2025</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G49" s="4">
         <v>0</v>
@@ -19676,7 +19702,7 @@
         <v>1079.7474130200001</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="N49" s="4">
         <v>1287478.7495154301</v>
@@ -19696,10 +19722,10 @@
       <c r="S49" s="4">
         <v>0</v>
       </c>
-      <c r="T49" s="8">
+      <c r="T49" s="7">
         <v>45200</v>
       </c>
-      <c r="U49" s="8">
+      <c r="U49" s="7">
         <v>45565</v>
       </c>
       <c r="V49" s="4" t="s">
@@ -19717,7 +19743,7 @@
       <c r="Z49" s="4">
         <v>1146.91679527</v>
       </c>
-      <c r="AA49" s="9">
+      <c r="AA49" s="8">
         <v>8.9082386462818602E-2</v>
       </c>
       <c r="AB49" s="4">
@@ -19746,62 +19772,62 @@
       </c>
       <c r="AJ49" s="4"/>
       <c r="AK49" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="AL49" s="4" t="s">
-        <v>550</v>
+        <v>545</v>
+      </c>
+      <c r="AL49" s="14" t="s">
+        <v>840</v>
       </c>
       <c r="AM49" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AN49" s="4" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AO49" s="4"/>
       <c r="AP49" s="4"/>
       <c r="AQ49" s="4"/>
       <c r="AR49" s="4"/>
       <c r="AS49" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AT49" s="4" t="s">
         <v>162</v>
       </c>
       <c r="AU49" s="4" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="AV49" s="4"/>
       <c r="AW49" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AX49" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AY49" s="4" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="AZ49" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="E50" s="4">
         <v>2025</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="G50" s="4">
         <v>367.75444922999998</v>
@@ -19822,7 +19848,7 @@
         <v>599.11121754999999</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="N50" s="4">
         <v>63290.880627400002</v>
@@ -19842,10 +19868,10 @@
       <c r="S50" s="4">
         <v>0</v>
       </c>
-      <c r="T50" s="8">
+      <c r="T50" s="7">
         <v>45200</v>
       </c>
-      <c r="U50" s="8">
+      <c r="U50" s="7">
         <v>45565</v>
       </c>
       <c r="V50" s="4" t="s">
@@ -19892,16 +19918,16 @@
       </c>
       <c r="AJ50" s="4"/>
       <c r="AK50" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="AL50" s="4" t="s">
-        <v>558</v>
+        <v>552</v>
+      </c>
+      <c r="AL50" s="14" t="s">
+        <v>839</v>
       </c>
       <c r="AM50" s="4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AN50" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AO50" s="4"/>
       <c r="AP50" s="4"/>
@@ -19911,37 +19937,37 @@
         <v>162</v>
       </c>
       <c r="AT50" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AU50" s="4" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="AV50" s="4"/>
       <c r="AW50" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AX50" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AY50" s="4" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="AZ50" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E51" s="4">
         <v>2025</v>
@@ -19977,7 +20003,7 @@
       <c r="AH51" s="4"/>
       <c r="AI51" s="4"/>
       <c r="AJ51" s="4" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="AK51" s="4"/>
       <c r="AL51" s="4"/>
@@ -19998,16 +20024,16 @@
     </row>
     <row r="52" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E52" s="4">
         <v>2025</v>
@@ -20026,7 +20052,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="N52" s="4">
         <v>33434.81</v>
@@ -20046,10 +20072,10 @@
       <c r="S52" s="4">
         <v>0</v>
       </c>
-      <c r="T52" s="8">
+      <c r="T52" s="7">
         <v>44927</v>
       </c>
-      <c r="U52" s="8">
+      <c r="U52" s="7">
         <v>45291</v>
       </c>
       <c r="V52" s="4" t="s">
@@ -20096,10 +20122,10 @@
       </c>
       <c r="AJ52" s="4"/>
       <c r="AK52" s="4" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="AL52" s="4" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="AM52" s="4"/>
       <c r="AN52" s="4"/>
@@ -20108,40 +20134,40 @@
       <c r="AQ52" s="4"/>
       <c r="AR52" s="4"/>
       <c r="AS52" s="4" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AT52" s="4" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AU52" s="4" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AV52" s="4"/>
       <c r="AW52" s="4" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="AX52" s="4" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="AY52" s="4" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="AZ52" s="4" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
     </row>
     <row r="53" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="E53" s="4">
         <v>2025</v>
@@ -20160,7 +20186,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="N53" s="4">
         <v>5008.07</v>
@@ -20180,10 +20206,10 @@
       <c r="S53" s="4">
         <v>0</v>
       </c>
-      <c r="T53" s="8">
+      <c r="T53" s="7">
         <v>44927</v>
       </c>
-      <c r="U53" s="8">
+      <c r="U53" s="7">
         <v>45291</v>
       </c>
       <c r="V53" s="4" t="s">
@@ -20230,10 +20256,10 @@
       </c>
       <c r="AJ53" s="4"/>
       <c r="AK53" s="4" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AL53" s="4" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="AM53" s="4"/>
       <c r="AN53" s="4"/>
@@ -20248,34 +20274,34 @@
         <v>110</v>
       </c>
       <c r="AU53" s="4" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="AV53" s="4"/>
       <c r="AW53" s="4" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="AX53" s="4" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="AY53" s="4" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="AZ53" s="4" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
     </row>
     <row r="54" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A54" s="4" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="E54" s="4">
         <v>2025</v>
@@ -20294,7 +20320,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="N54" s="4">
         <v>64676.800000000003</v>
@@ -20314,10 +20340,10 @@
       <c r="S54" s="4">
         <v>0</v>
       </c>
-      <c r="T54" s="8">
+      <c r="T54" s="7">
         <v>44927</v>
       </c>
-      <c r="U54" s="8">
+      <c r="U54" s="7">
         <v>45291</v>
       </c>
       <c r="V54" s="4" t="s">
@@ -20364,10 +20390,10 @@
       </c>
       <c r="AJ54" s="4"/>
       <c r="AK54" s="4" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="AL54" s="4" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="AM54" s="4"/>
       <c r="AN54" s="4"/>
@@ -20376,40 +20402,40 @@
       <c r="AQ54" s="4"/>
       <c r="AR54" s="4"/>
       <c r="AS54" s="4" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AT54" s="4" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AU54" s="4" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="AV54" s="4"/>
       <c r="AW54" s="4" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="AX54" s="4" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="AY54" s="4" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="AZ54" s="4" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="55" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A55" s="4" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E55" s="4">
         <v>2025</v>
@@ -20428,7 +20454,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="N55" s="4">
         <v>2623.05</v>
@@ -20448,10 +20474,10 @@
       <c r="S55" s="4">
         <v>0</v>
       </c>
-      <c r="T55" s="8">
+      <c r="T55" s="7">
         <v>44927</v>
       </c>
-      <c r="U55" s="8">
+      <c r="U55" s="7">
         <v>45291</v>
       </c>
       <c r="V55" s="4" t="s">
@@ -20498,10 +20524,10 @@
       </c>
       <c r="AJ55" s="4"/>
       <c r="AK55" s="4" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="AL55" s="4" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="AM55" s="4"/>
       <c r="AN55" s="4"/>
@@ -20510,40 +20536,40 @@
       <c r="AQ55" s="4"/>
       <c r="AR55" s="4"/>
       <c r="AS55" s="4" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AT55" s="4" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="AU55" s="4" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="AV55" s="4"/>
       <c r="AW55" s="4" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="AX55" s="4" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="AY55" s="4" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="AZ55" s="4" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
     </row>
     <row r="56" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A56" s="4" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E56" s="4">
         <v>2025</v>
@@ -20579,7 +20605,7 @@
       <c r="AH56" s="4"/>
       <c r="AI56" s="4"/>
       <c r="AJ56" s="4" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="AK56" s="4"/>
       <c r="AL56" s="4"/>
@@ -20600,16 +20626,16 @@
     </row>
     <row r="57" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A57" s="4" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="E57" s="4">
         <v>2025</v>
@@ -20645,7 +20671,7 @@
       <c r="AH57" s="4"/>
       <c r="AI57" s="4"/>
       <c r="AJ57" s="4" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="AK57" s="4"/>
       <c r="AL57" s="4"/>
@@ -20666,22 +20692,22 @@
     </row>
     <row r="58" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A58" s="4" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="E58" s="4">
         <v>2025</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -20696,7 +20722,7 @@
         <v>2.98</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="N58" s="4">
         <v>278.07</v>
@@ -20716,10 +20742,10 @@
       <c r="S58" s="4">
         <v>0</v>
       </c>
-      <c r="T58" s="8">
+      <c r="T58" s="7">
         <v>45200</v>
       </c>
-      <c r="U58" s="8">
+      <c r="U58" s="7">
         <v>45565</v>
       </c>
       <c r="V58" s="4" t="s">
@@ -20766,10 +20792,10 @@
       </c>
       <c r="AJ58" s="4"/>
       <c r="AK58" s="4" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="AL58" s="4" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="AM58" s="4"/>
       <c r="AN58" s="4"/>
@@ -20791,39 +20817,39 @@
         <v>327</v>
       </c>
       <c r="AV58" s="4" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="AW58" s="4" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="AX58" s="4" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="AY58" s="4" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="AZ58" s="4" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="59" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A59" s="4" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="E59" s="4">
         <v>2025</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -20838,7 +20864,7 @@
         <v>58.68</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="N59" s="4">
         <v>1201.47</v>
@@ -20858,10 +20884,10 @@
       <c r="S59" s="4">
         <v>0</v>
       </c>
-      <c r="T59" s="8">
+      <c r="T59" s="7">
         <v>45200</v>
       </c>
-      <c r="U59" s="8">
+      <c r="U59" s="7">
         <v>45565</v>
       </c>
       <c r="V59" s="4" t="s">
@@ -20908,10 +20934,10 @@
       </c>
       <c r="AJ59" s="4"/>
       <c r="AK59" s="4" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="AL59" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="AM59" s="4"/>
       <c r="AN59" s="4"/>
@@ -20933,39 +20959,39 @@
         <v>327</v>
       </c>
       <c r="AV59" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="AW59" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="AX59" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="AY59" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="AZ59" s="4" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="60" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A60" s="4" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E60" s="4">
         <v>2025</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="G60" s="4">
         <v>0</v>
@@ -20986,7 +21012,7 @@
         <v>61.72</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="N60" s="4">
         <v>132.83000000000001</v>
@@ -21006,10 +21032,10 @@
       <c r="S60" s="4">
         <v>0</v>
       </c>
-      <c r="T60" s="8">
+      <c r="T60" s="7">
         <v>45200</v>
       </c>
-      <c r="U60" s="8">
+      <c r="U60" s="7">
         <v>45565</v>
       </c>
       <c r="V60" s="4" t="s">
@@ -21056,10 +21082,10 @@
       </c>
       <c r="AJ60" s="4"/>
       <c r="AK60" s="4" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="AL60" s="4" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="AM60" s="4" t="s">
         <v>211</v>
@@ -21085,33 +21111,33 @@
         <v>327</v>
       </c>
       <c r="AV60" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="AW60" s="4" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="AX60" s="4" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="AY60" s="4" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="AZ60" s="4" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="61" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A61" s="4" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="E61" s="4">
         <v>2025</v>
@@ -21136,7 +21162,7 @@
         <v>190.02</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="N61" s="4">
         <v>22925.06</v>
@@ -21156,10 +21182,10 @@
       <c r="S61" s="4">
         <v>0</v>
       </c>
-      <c r="T61" s="8">
+      <c r="T61" s="7">
         <v>44743</v>
       </c>
-      <c r="U61" s="8">
+      <c r="U61" s="7">
         <v>45107</v>
       </c>
       <c r="V61" s="4" t="s">
@@ -21206,10 +21232,10 @@
       </c>
       <c r="AJ61" s="4"/>
       <c r="AK61" s="4" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="AL61" s="4" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="AM61" s="4" t="s">
         <v>211</v>
@@ -21231,39 +21257,39 @@
         <v>327</v>
       </c>
       <c r="AV61" s="4" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="AW61" s="4" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="AX61" s="4" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="AY61" s="4" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="AZ61" s="4" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
     </row>
     <row r="62" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A62" s="4" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E62" s="4">
         <v>2025</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="G62" s="4">
         <v>0</v>
@@ -21284,7 +21310,7 @@
         <v>312.05</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="N62" s="4">
         <v>4245</v>
@@ -21304,10 +21330,10 @@
       <c r="S62" s="4">
         <v>0</v>
       </c>
-      <c r="T62" s="8">
+      <c r="T62" s="7">
         <v>42339</v>
       </c>
-      <c r="U62" s="8">
+      <c r="U62" s="7">
         <v>43130</v>
       </c>
       <c r="V62" s="4" t="s">
@@ -21354,62 +21380,62 @@
       </c>
       <c r="AJ62" s="4"/>
       <c r="AK62" s="4" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="AL62" s="4" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="AM62" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AN62" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AO62" s="4"/>
       <c r="AP62" s="4"/>
       <c r="AQ62" s="4"/>
       <c r="AR62" s="4"/>
       <c r="AS62" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AT62" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AU62" s="4" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="AV62" s="4"/>
       <c r="AW62" s="4" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="AX62" s="4" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="AY62" s="4" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="AZ62" s="4" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="63" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A63" s="4" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="E63" s="4">
         <v>2025</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -21441,7 +21467,7 @@
       <c r="AH63" s="4"/>
       <c r="AI63" s="4"/>
       <c r="AJ63" s="4" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="AK63" s="4"/>
       <c r="AL63" s="4"/>
@@ -21462,16 +21488,16 @@
     </row>
     <row r="64" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A64" s="4" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E64" s="4">
         <v>2025</v>
@@ -21496,7 +21522,7 @@
         <v>1035.17</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="N64" s="4">
         <v>19914</v>
@@ -21516,10 +21542,10 @@
       <c r="S64" s="4">
         <v>0</v>
       </c>
-      <c r="T64" s="8">
+      <c r="T64" s="7">
         <v>42917</v>
       </c>
-      <c r="U64" s="8">
+      <c r="U64" s="7">
         <v>43281</v>
       </c>
       <c r="V64" s="4" t="s">
@@ -21566,62 +21592,62 @@
       </c>
       <c r="AJ64" s="4"/>
       <c r="AK64" s="4" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="AL64" s="4" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="AM64" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AN64" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AO64" s="4"/>
       <c r="AP64" s="4"/>
       <c r="AQ64" s="4"/>
       <c r="AR64" s="4"/>
       <c r="AS64" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AT64" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AU64" s="4" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="AV64" s="4"/>
       <c r="AW64" s="4" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="AX64" s="4" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="AY64" s="4" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="AZ64" s="4" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
     </row>
     <row r="65" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A65" s="4" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="E65" s="4">
         <v>2025</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -21642,7 +21668,7 @@
         <v>14.95</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="N65" s="4">
         <v>185.78</v>
@@ -21662,10 +21688,10 @@
       <c r="S65" s="4">
         <v>0</v>
       </c>
-      <c r="T65" s="8">
+      <c r="T65" s="7">
         <v>45200</v>
       </c>
-      <c r="U65" s="8">
+      <c r="U65" s="7">
         <v>45565</v>
       </c>
       <c r="V65" s="4" t="s">
@@ -21712,10 +21738,10 @@
       </c>
       <c r="AJ65" s="4"/>
       <c r="AK65" s="4" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="AL65" s="4" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="AM65" s="4" t="s">
         <v>211</v>
@@ -21741,33 +21767,33 @@
         <v>327</v>
       </c>
       <c r="AV65" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="AW65" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="AX65" s="4" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="AY65" s="4" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="AZ65" s="4" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="66" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A66" s="4" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="E66" s="4">
         <v>2025</v>
@@ -21792,7 +21818,7 @@
         <v>324.72000000000003</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="N66" s="4">
         <v>5914</v>
@@ -21812,10 +21838,10 @@
       <c r="S66" s="4">
         <v>0</v>
       </c>
-      <c r="T66" s="8">
+      <c r="T66" s="7">
         <v>42917</v>
       </c>
-      <c r="U66" s="8">
+      <c r="U66" s="7">
         <v>43281</v>
       </c>
       <c r="V66" s="4" t="s">
@@ -21862,56 +21888,56 @@
       </c>
       <c r="AJ66" s="4"/>
       <c r="AK66" s="4" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="AL66" s="4" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="AM66" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AN66" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AO66" s="4"/>
       <c r="AP66" s="4"/>
       <c r="AQ66" s="4"/>
       <c r="AR66" s="4"/>
       <c r="AS66" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AT66" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AU66" s="4" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="AV66" s="4"/>
       <c r="AW66" s="4" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="AX66" s="4" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="AY66" s="4" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="AZ66" s="4" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
     <row r="67" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A67" s="4" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="E67" s="4">
         <v>2025</v>
@@ -21936,7 +21962,7 @@
         <v>8662.0499999999993</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="N67" s="4">
         <v>93509.72</v>
@@ -21956,10 +21982,10 @@
       <c r="S67" s="4">
         <v>0</v>
       </c>
-      <c r="T67" s="8">
+      <c r="T67" s="7">
         <v>45200</v>
       </c>
-      <c r="U67" s="8">
+      <c r="U67" s="7">
         <v>45565</v>
       </c>
       <c r="V67" s="4" t="s">
@@ -22006,10 +22032,10 @@
       </c>
       <c r="AJ67" s="4"/>
       <c r="AK67" s="4" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="AL67" s="4" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="AM67" s="4" t="s">
         <v>111</v>
@@ -22028,40 +22054,40 @@
         <v>111</v>
       </c>
       <c r="AU67" s="4" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="AV67" s="4"/>
       <c r="AW67" s="4" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="AX67" s="4" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="AY67" s="4" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="AZ67" s="4" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="68" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A68" s="4" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="E68" s="4">
         <v>2025</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="G68" s="4">
         <v>0</v>
@@ -22082,7 +22108,7 @@
         <v>96.39</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="N68" s="4">
         <v>2053.35</v>
@@ -22102,10 +22128,10 @@
       <c r="S68" s="4">
         <v>33.44</v>
       </c>
-      <c r="T68" s="8">
+      <c r="T68" s="7">
         <v>45200</v>
       </c>
-      <c r="U68" s="8">
+      <c r="U68" s="7">
         <v>45565</v>
       </c>
       <c r="V68" s="4" t="s">
@@ -22126,7 +22152,7 @@
       <c r="AA68" s="4">
         <v>4.69428007889546</v>
       </c>
-      <c r="AB68" s="9">
+      <c r="AB68" s="8">
         <v>2.5811478802931699E-2</v>
       </c>
       <c r="AC68" s="4">
@@ -22152,10 +22178,10 @@
       </c>
       <c r="AJ68" s="4"/>
       <c r="AK68" s="4" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="AL68" s="4" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="AM68" s="4" t="s">
         <v>393</v>
@@ -22176,46 +22202,46 @@
         <v>211</v>
       </c>
       <c r="AS68" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AT68" s="4" t="s">
         <v>393</v>
       </c>
       <c r="AU68" s="4" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="AV68" s="4"/>
       <c r="AW68" s="4" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="AX68" s="4" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="AY68" s="4" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="AZ68" s="4" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
     </row>
     <row r="69" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A69" s="4" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="E69" s="4">
         <v>2025</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="G69" s="4">
         <v>0</v>
@@ -22236,7 +22262,7 @@
         <v>480.74</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="N69" s="4">
         <v>157452.95000000001</v>
@@ -22256,10 +22282,10 @@
       <c r="S69" s="4">
         <v>1480.98</v>
       </c>
-      <c r="T69" s="8">
+      <c r="T69" s="7">
         <v>45200</v>
       </c>
-      <c r="U69" s="8">
+      <c r="U69" s="7">
         <v>45565</v>
       </c>
       <c r="V69" s="4" t="s">
@@ -22306,10 +22332,10 @@
       </c>
       <c r="AJ69" s="4"/>
       <c r="AK69" s="4" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="AL69" s="4" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="AM69" s="4" t="s">
         <v>296</v>
@@ -22332,40 +22358,40 @@
         <v>296</v>
       </c>
       <c r="AU69" s="4" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="AV69" s="4"/>
       <c r="AW69" s="4" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="AX69" s="4" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="AY69" s="4" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="AZ69" s="4" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="70" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A70" s="4" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E70" s="4">
         <v>2025</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -22380,7 +22406,7 @@
         <v>13.87</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N70" s="4">
         <v>1333.36</v>
@@ -22400,10 +22426,10 @@
       <c r="S70" s="4">
         <v>69.94</v>
       </c>
-      <c r="T70" s="8">
+      <c r="T70" s="7">
         <v>45200</v>
       </c>
-      <c r="U70" s="8">
+      <c r="U70" s="7">
         <v>45565</v>
       </c>
       <c r="V70" s="4" t="s">
@@ -22430,7 +22456,7 @@
       <c r="AC70" s="4">
         <v>5.2453950920981498</v>
       </c>
-      <c r="AD70" s="9">
+      <c r="AD70" s="8">
         <v>8.4748305033899296E-2</v>
       </c>
       <c r="AE70" s="4">
@@ -22450,10 +22476,10 @@
       </c>
       <c r="AJ70" s="4"/>
       <c r="AK70" s="4" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="AL70" s="4" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="AM70" s="4"/>
       <c r="AN70" s="4"/>
@@ -22476,40 +22502,40 @@
         <v>111</v>
       </c>
       <c r="AU70" s="4" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="AV70" s="4"/>
       <c r="AW70" s="4" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="AX70" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="AY70" s="4" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="AZ70" s="4" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
     </row>
     <row r="71" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A71" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E71" s="4">
         <v>2025</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -22530,7 +22556,7 @@
         <v>272.29000000000002</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="N71" s="4">
         <v>3549.89</v>
@@ -22550,10 +22576,10 @@
       <c r="S71" s="4">
         <v>43.72</v>
       </c>
-      <c r="T71" s="8">
+      <c r="T71" s="7">
         <v>45200</v>
       </c>
-      <c r="U71" s="8">
+      <c r="U71" s="7">
         <v>45565</v>
       </c>
       <c r="V71" s="4" t="s">
@@ -22600,66 +22626,66 @@
       </c>
       <c r="AJ71" s="4"/>
       <c r="AK71" s="4" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="AL71" s="4" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="AM71" s="4" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="AN71" s="4" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="AO71" s="4"/>
       <c r="AP71" s="4"/>
       <c r="AQ71" s="4" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="AR71" s="4" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="AS71" s="4" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="AT71" s="4" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="AU71" s="4" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="AV71" s="4"/>
       <c r="AW71" s="4" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="AX71" s="4" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="AY71" s="4" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="AZ71" s="4" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="72" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A72" s="4" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="E72" s="4">
         <v>2025</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="G72" s="4">
         <v>0</v>
@@ -22680,7 +22706,7 @@
         <v>77.08</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="N72" s="4">
         <v>7330.11</v>
@@ -22700,10 +22726,10 @@
       <c r="S72" s="4">
         <v>45.84</v>
       </c>
-      <c r="T72" s="8">
+      <c r="T72" s="7">
         <v>45200</v>
       </c>
-      <c r="U72" s="8">
+      <c r="U72" s="7">
         <v>45565</v>
       </c>
       <c r="V72" s="4" t="s">
@@ -22724,7 +22750,7 @@
       <c r="AA72" s="4">
         <v>1.05155311448259</v>
       </c>
-      <c r="AB72" s="9">
+      <c r="AB72" s="8">
         <v>2.4829095334176401E-2</v>
       </c>
       <c r="AC72" s="4">
@@ -22750,22 +22776,22 @@
       </c>
       <c r="AJ72" s="4"/>
       <c r="AK72" s="4" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="AL72" s="4" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="AM72" s="4" t="s">
         <v>211</v>
       </c>
       <c r="AN72" s="4" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="AO72" s="4" t="s">
         <v>211</v>
       </c>
       <c r="AP72" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AQ72" s="4" t="s">
         <v>211</v>
@@ -22777,43 +22803,43 @@
         <v>211</v>
       </c>
       <c r="AT72" s="4" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="AU72" s="4" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="AV72" s="4"/>
       <c r="AW72" s="4" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="AX72" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="AY72" s="4" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="AZ72" s="4" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
     </row>
     <row r="73" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A73" s="4" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="E73" s="4">
         <v>2025</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
@@ -22828,7 +22854,7 @@
         <v>0.93</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="N73" s="4">
         <v>3939.2</v>
@@ -22848,10 +22874,10 @@
       <c r="S73" s="4">
         <v>23.42</v>
       </c>
-      <c r="T73" s="8">
+      <c r="T73" s="7">
         <v>45200</v>
       </c>
-      <c r="U73" s="8">
+      <c r="U73" s="7">
         <v>45565</v>
       </c>
       <c r="V73" s="4" t="s">
@@ -22869,7 +22895,7 @@
       <c r="Z73" s="4">
         <v>0.93</v>
       </c>
-      <c r="AA73" s="9">
+      <c r="AA73" s="8">
         <v>2.3608854589764399E-2</v>
       </c>
       <c r="AB73" s="4">
@@ -22887,7 +22913,7 @@
       <c r="AF73" s="4">
         <v>0.93</v>
       </c>
-      <c r="AG73" s="9">
+      <c r="AG73" s="8">
         <v>2.3608854589764399E-2</v>
       </c>
       <c r="AH73" s="4">
@@ -22898,10 +22924,10 @@
       </c>
       <c r="AJ73" s="4"/>
       <c r="AK73" s="4" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="AL73" s="4" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="AM73" s="4"/>
       <c r="AN73" s="4"/>
@@ -22916,40 +22942,40 @@
         <v>211</v>
       </c>
       <c r="AU73" s="4" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="AV73" s="4"/>
       <c r="AW73" s="4" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="AX73" s="4" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="AY73" s="4" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="AZ73" s="4" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="74" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A74" s="4" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E74" s="4">
         <v>2025</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="G74" s="4">
         <v>0</v>
@@ -22970,7 +22996,7 @@
         <v>552.15</v>
       </c>
       <c r="M74" s="4" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="N74" s="4">
         <v>25444.18</v>
@@ -22990,10 +23016,10 @@
       <c r="S74" s="4">
         <v>40.19</v>
       </c>
-      <c r="T74" s="8">
+      <c r="T74" s="7">
         <v>45200</v>
       </c>
-      <c r="U74" s="8">
+      <c r="U74" s="7">
         <v>45565</v>
       </c>
       <c r="V74" s="4" t="s">
@@ -23014,7 +23040,7 @@
       <c r="AA74" s="4">
         <v>2.1700443873608801</v>
       </c>
-      <c r="AB74" s="9">
+      <c r="AB74" s="8">
         <v>6.0288836189651203E-2</v>
       </c>
       <c r="AC74" s="4">
@@ -23040,10 +23066,10 @@
       </c>
       <c r="AJ74" s="4"/>
       <c r="AK74" s="4" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="AL74" s="4" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="AM74" s="4" t="s">
         <v>127</v>
@@ -23060,26 +23086,26 @@
         <v>211</v>
       </c>
       <c r="AS74" s="4" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="AT74" s="4" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="AU74" s="4" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="AV74" s="4"/>
       <c r="AW74" s="4" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="AX74" s="4" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="AY74" s="4" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="AZ74" s="4" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="75" spans="1:52" x14ac:dyDescent="0.45">
